--- a/Historias_De_Usuario_FutbolZone_ADSO.xlsx
+++ b/Historias_De_Usuario_FutbolZone_ADSO.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,30 +34,30 @@
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="16"/>
+      <sz val="15"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <color rgb="00E2E8F0"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00059669"/>
-      <sz val="22"/>
+      <sz val="20"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00475569"/>
-      <sz val="9"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="000F172A"/>
-      <sz val="13"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -69,12 +69,12 @@
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="001E293B"/>
-      <sz val="10"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <color rgb="001E293B"/>
-      <sz val="10"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -91,6 +91,12 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
       <color rgb="000284C7"/>
       <sz val="9"/>
     </font>
@@ -101,7 +107,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -142,6 +148,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="000284C7"/>
         <bgColor rgb="000284C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
@@ -191,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -221,6 +233,9 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -228,6 +243,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -261,25 +279,28 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -648,16 +669,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
     <col width="48" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -672,7 +693,7 @@
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Programa: Análisis y Desarrollo de Software (ADSO) | SENA 2026 | Backlog Oficial</t>
+          <t>Programa: Análisis y Desarrollo de Software (ADSO) | SENA Trimestre III | Avance Actual: 75% MVP</t>
         </is>
       </c>
     </row>
@@ -691,11 +712,11 @@
         <v/>
       </c>
       <c r="F6" s="3">
-        <f>'📋 Backlog General'!C6</f>
+        <f>'📋 Backlog General'!I4</f>
         <v/>
       </c>
       <c r="H6" s="4">
-        <f>'📋 Backlog General'!C5</f>
+        <f>'📋 Backlog General'!E4</f>
         <v/>
       </c>
     </row>
@@ -703,32 +724,32 @@
     <row r="8">
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>TOTAL HISTORIAS (HU)
+          <t>TOTAL HISTORIAS
 (38 HUs Planificadas)</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>HU CLIENTE
-(Módulo de Jugadores)</t>
+(20 HUs (75% Listas))</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
           <t>HU ADMIN
-(Módulo de Gestión)</t>
+(18 HUs (77% Listas))</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>PUNTOS DE HISTORIA
-(Esfuerzo Total Ágil)</t>
+          <t>PUNTOS DESARROLLADOS
+(Puntos de Historia Listos)</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>% AVANCE GLOBAL
-(Cálculo Automático)</t>
+          <t>% AVANCE PROYECTO
+(Fase MVP Completada)</t>
         </is>
       </c>
     </row>
@@ -736,7 +757,7 @@
     <row r="10">
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>📌 RESUMEN DE DESARROLLO POR MÓDULOS</t>
+          <t>📌 ESTADO DE AVANCE POR MÓDULOS DEL SISTEMA</t>
         </is>
       </c>
     </row>
@@ -758,12 +779,12 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>HUs Listas</t>
+          <t>Completadas</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Puntos</t>
+          <t>Pendientes</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -773,7 +794,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Estado Actual</t>
         </is>
       </c>
     </row>
@@ -789,61 +810,57 @@
         </is>
       </c>
       <c r="D12" s="10">
-        <f>COUNTIF('📋 Backlog General'!E10:E47, "Autenticación") + COUNTIF('📋 Backlog General'!E10:E47, "Seguridad") + COUNTIF('📋 Backlog General'!E10:E47, "Infraestructura")</f>
+        <f>COUNTIF('📋 Backlog General'!E10:E47, "Autenticación") + COUNTIF('📋 Backlog General'!E10:E47, "Seguridad")</f>
         <v/>
       </c>
       <c r="E12" s="10">
-        <f>COUNTIF('📋 Backlog General'!E10:E47, "Autenticación") + COUNTIF('📋 Backlog General'!E10:E47, "Seguridad") + COUNTIF('📋 Backlog General'!E10:E47, "Infraestructura")</f>
+        <f>COUNTIFS('📋 Backlog General'!E10:E47, "Autenticación", '📋 Backlog General'!I10:I47, "Completado") + COUNTIFS('📋 Backlog General'!E10:E47, "Seguridad", '📋 Backlog General'!I10:I47, "Completado")</f>
         <v/>
       </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>🟢 Completado</t>
+      <c r="F12" s="10">
+        <f>D12-E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="11">
+        <f>E12/D12</f>
+        <v/>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>🟢 100% Funcional</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Módulo 2: Catálogo de Canchas &amp; Filtros</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>Cliente / Admin</t>
         </is>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="14">
         <f>COUNTIF('📋 Backlog General'!E10:E47, "Canchas")</f>
         <v/>
       </c>
-      <c r="E13" s="13">
-        <f>COUNTIF('📋 Backlog General'!E10:E47, "Canchas")</f>
+      <c r="E13" s="14">
+        <f>COUNTIFS('📋 Backlog General'!E10:E47, "Canchas", '📋 Backlog General'!I10:I47, "Completado")</f>
         <v/>
       </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="14" t="inlineStr">
-        <is>
-          <t>🟢 Completado</t>
+      <c r="F13" s="14">
+        <f>D13-E13</f>
+        <v/>
+      </c>
+      <c r="G13" s="15">
+        <f>E13/D13</f>
+        <v/>
+      </c>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t>🟢 100% Funcional</t>
         </is>
       </c>
     </row>
@@ -863,196 +880,187 @@
         <v/>
       </c>
       <c r="E14" s="10">
-        <f>COUNTIF('📋 Backlog General'!E10:E47, "Reservas") + COUNTIF('📋 Backlog General'!E10:E47, "Agendamiento")</f>
+        <f>COUNTIFS('📋 Backlog General'!E10:E47, "Reservas", '📋 Backlog General'!I10:I47, "Completado") + COUNTIFS('📋 Backlog General'!E10:E47, "Agendamiento", '📋 Backlog General'!I10:I47, "Completado")</f>
         <v/>
       </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H14" s="11" t="inlineStr">
-        <is>
-          <t>🟢 Completado</t>
+      <c r="F14" s="10">
+        <f>D14-E14</f>
+        <v/>
+      </c>
+      <c r="G14" s="11">
+        <f>E14/D14</f>
+        <v/>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>🟢 100% Funcional</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>Módulo 4: Torneos Deportivos &amp; Inscripción</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Módulo 4: Dashboard Admin, Personal &amp; Reportes</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="D15" s="14">
+        <f>COUNTIF('📋 Backlog General'!E10:E47, "Administración") + COUNTIF('📋 Backlog General'!E10:E47, "Personal") + COUNTIF('📋 Backlog General'!E10:E47, "Reportes")</f>
+        <v/>
+      </c>
+      <c r="E15" s="14">
+        <f>COUNTIFS('📋 Backlog General'!E10:E47, "Administración", '📋 Backlog General'!I10:I47, "Completado") + COUNTIFS('📋 Backlog General'!E10:E47, "Personal", '📋 Backlog General'!I10:I47, "Completado") + COUNTIFS('📋 Backlog General'!E10:E47, "Reportes", '📋 Backlog General'!I10:I47, "Completado")</f>
+        <v/>
+      </c>
+      <c r="F15" s="14">
+        <f>D15-E15</f>
+        <v/>
+      </c>
+      <c r="G15" s="15">
+        <f>E15/D15</f>
+        <v/>
+      </c>
+      <c r="H15" s="16" t="inlineStr">
+        <is>
+          <t>🟢 100% Funcional</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Módulo 5: UI/UX (Dock 3 Botones, Móvil &amp; Tema)</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="D16" s="10">
+        <f>COUNTIF('📋 Backlog General'!E10:E47, "UI / UX")</f>
+        <v/>
+      </c>
+      <c r="E16" s="10">
+        <f>COUNTIFS('📋 Backlog General'!E10:E47, "UI / UX", '📋 Backlog General'!I10:I47, "Completado")</f>
+        <v/>
+      </c>
+      <c r="F16" s="10">
+        <f>D16-E16</f>
+        <v/>
+      </c>
+      <c r="G16" s="11">
+        <f>E16/D16</f>
+        <v/>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>🟢 100% Funcional</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>Módulo 6: Torneos Deportivos</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>Cliente / Admin</t>
         </is>
       </c>
-      <c r="D15" s="13">
+      <c r="D17" s="14">
         <f>COUNTIF('📋 Backlog General'!E10:E47, "Torneos")</f>
         <v/>
       </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="H15" s="14" t="inlineStr">
-        <is>
-          <t>🟢 Operativo</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Módulo 5: Dashboard Admin &amp; Personal</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Administrador</t>
-        </is>
-      </c>
-      <c r="D16" s="10">
-        <f>COUNTIF('📋 Backlog General'!E10:E47, "Administración") + COUNTIF('📋 Backlog General'!E10:E47, "Personal") + COUNTIF('📋 Backlog General'!E10:E47, "Reportes")</f>
+      <c r="E17" s="14">
+        <f>COUNTIFS('📋 Backlog General'!E10:E47, "Torneos", '📋 Backlog General'!I10:I47, "Completado")</f>
         <v/>
       </c>
-      <c r="E16" s="10">
-        <f>COUNTIF('📋 Backlog General'!E10:E47, "Administración") + COUNTIF('📋 Backlog General'!E10:E47, "Personal") + COUNTIF('📋 Backlog General'!E10:E47, "Reportes")</f>
+      <c r="F17" s="14">
+        <f>D17-E17</f>
         <v/>
       </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H16" s="11" t="inlineStr">
-        <is>
-          <t>🟢 Completado</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>Módulo 6: UI/UX (Dock 3 Botones / Móvil / Tema)</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="D17" s="13">
-        <f>COUNTIF('📋 Backlog General'!E10:E47, "UI / UX") + COUNTIF('📋 Backlog General'!E10:E47, "Comunidad") + COUNTIF('📋 Backlog General'!E10:E47, "Reseñas")</f>
+      <c r="G17" s="15">
+        <f>E17/D17</f>
         <v/>
       </c>
-      <c r="E17" s="13">
-        <f>COUNTIF('📋 Backlog General'!E10:E47, "UI / UX") + COUNTIF('📋 Backlog General'!E10:E47, "Comunidad") + COUNTIF('📋 Backlog General'!E10:E47, "Reseñas")</f>
-        <v/>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H17" s="14" t="inlineStr">
-        <is>
-          <t>🟢 Completado</t>
+      <c r="H17" s="16" t="inlineStr">
+        <is>
+          <t>🟡 75% Operativo</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Módulo 7: Base de Datos SQLite &amp; ORM</t>
+          <t>Módulo 7: Pasarela de Pagos &amp; Cloud (Fase Final)</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIF('📋 Backlog General'!E10:E47, "Arquitectura")</f>
+        <f>COUNTIF('📋 Backlog General'!E10:E47, "Pagos") + COUNTIF('📋 Backlog General'!E10:E47, "Comprobantes") + COUNTIF('📋 Backlog General'!E10:E47, "Notificaciones") + COUNTIF('📋 Backlog General'!E10:E47, "Fidelización") + COUNTIF('📋 Backlog General'!E10:E47, "Integraciones") + COUNTIF('📋 Backlog General'!E10:E47, "DevOps")</f>
         <v/>
       </c>
-      <c r="E18" s="10">
-        <f>COUNTIF('📋 Backlog General'!E10:E47, "Arquitectura")</f>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="10">
+        <f>D18</f>
         <v/>
       </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>🟢 Completado</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>⏳ En Progreso</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>TOTAL CONSOLIDADO DEL SISTEMA</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>SISTEMA COMPLETO</t>
         </is>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="18">
         <f>SUM(D12:D18)</f>
         <v/>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="18">
         <f>SUM(E12:E18)</f>
         <v/>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="18">
         <f>SUM(F12:F18)</f>
         <v/>
       </c>
-      <c r="G19" s="17">
-        <f>AVERAGE(G12:G18)</f>
+      <c r="G19" s="19">
+        <f>E19/D19</f>
         <v/>
       </c>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>🚀 98% LISTO</t>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>🎯 75% MVP LISTO</t>
         </is>
       </c>
     </row>
@@ -1083,16 +1091,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="48" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
@@ -1101,47 +1109,47 @@
   <sheetData>
     <row r="1"/>
     <row r="2">
-      <c r="B2" s="19" t="inlineStr">
-        <is>
-          <t>👤 HISTORIAS DE USUARIO — MÓDULO CLIENTE &amp; JUGADORES</t>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>👤 HISTORIAS DE USUARIO — MÓDULO CLIENTE &amp; JUGADORES (75% AVANCE)</t>
         </is>
       </c>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>Total HUs Cliente:</t>
         </is>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="23">
         <f>COUNTA(B10:B29)</f>
         <v/>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="22" t="inlineStr">
         <is>
           <t>Completadas:</t>
         </is>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="23">
         <f>COUNTIF(H10:H29, "Completado")</f>
         <v/>
       </c>
-      <c r="F4" s="20" t="inlineStr">
+      <c r="F4" s="22" t="inlineStr">
         <is>
           <t>% Avance Cliente:</t>
         </is>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="24">
         <f>E4/C4</f>
         <v/>
       </c>
-      <c r="H4" s="20" t="inlineStr">
+      <c r="H4" s="22" t="inlineStr">
         <is>
           <t>Puntos Totales:</t>
         </is>
       </c>
-      <c r="I4" s="21">
+      <c r="I4" s="23">
         <f>SUM(F10:F29)</f>
         <v/>
       </c>
@@ -1151,69 +1159,69 @@
     <row r="7"/>
     <row r="8"/>
     <row r="9">
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>Título de la Historia</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>Módulo</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t>Prioridad</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="25" t="inlineStr">
         <is>
           <t>Puntos</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t>Sprint</t>
         </is>
       </c>
-      <c r="H9" s="23" t="inlineStr">
+      <c r="H9" s="25" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="I9" s="23" t="inlineStr">
+      <c r="I9" s="25" t="inlineStr">
         <is>
           <t>% Avance</t>
         </is>
       </c>
-      <c r="J9" s="23" t="inlineStr">
+      <c r="J9" s="25" t="inlineStr">
         <is>
           <t>Descripción (Como / Quiero / Para)</t>
         </is>
       </c>
-      <c r="K9" s="23" t="inlineStr">
+      <c r="K9" s="25" t="inlineStr">
         <is>
           <t>Endpoint API Backend</t>
         </is>
       </c>
-      <c r="L9" s="23" t="inlineStr">
+      <c r="L9" s="25" t="inlineStr">
         <is>
           <t>Componente Frontend</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>HU-01</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>Registro de Cuenta de Cliente</t>
         </is>
@@ -1236,94 +1244,94 @@
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="H10" s="25" t="inlineStr">
+      <c r="H10" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J10" s="24" t="inlineStr">
+      <c r="J10" s="26" t="inlineStr">
         <is>
           <t>Como visitante, quiero registrar mis datos con nombre, correo y clave, para tener una cuenta y reservar canchas.</t>
         </is>
       </c>
-      <c r="K10" s="24" t="inlineStr">
+      <c r="K10" s="26" t="inlineStr">
         <is>
           <t>POST /api/usuarios/registro</t>
         </is>
       </c>
-      <c r="L10" s="24" t="inlineStr">
+      <c r="L10" s="26" t="inlineStr">
         <is>
           <t>LoginModal.tsx</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>HU-02</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>Inicio de Sesión con JWT</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>Seguridad</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="G11" s="13" t="inlineStr">
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="H11" s="25" t="inlineStr">
+      <c r="H11" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I11" s="16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J11" s="26" t="inlineStr">
+      <c r="J11" s="28" t="inlineStr">
         <is>
           <t>Como cliente, quiero iniciar sesión con mi correo y contraseña, para acceder a mis reservas y perfil.</t>
         </is>
       </c>
-      <c r="K11" s="26" t="inlineStr">
+      <c r="K11" s="28" t="inlineStr">
         <is>
           <t>POST /api/usuarios/login</t>
         </is>
       </c>
-      <c r="L11" s="26" t="inlineStr">
+      <c r="L11" s="28" t="inlineStr">
         <is>
           <t>LoginModal.tsx</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>HU-03</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>Recuperación de Contraseña con PIN Gmail</t>
         </is>
@@ -1346,94 +1354,94 @@
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="H12" s="25" t="inlineStr">
+      <c r="H12" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J12" s="24" t="inlineStr">
+      <c r="J12" s="26" t="inlineStr">
         <is>
           <t>Como cliente que olvidó su clave, quiero recibir un PIN de 6 dígitos en mi Gmail real, para restablecer mi acceso.</t>
         </is>
       </c>
-      <c r="K12" s="24" t="inlineStr">
+      <c r="K12" s="26" t="inlineStr">
         <is>
           <t>POST /api/auth/recuperar-password/*</t>
         </is>
       </c>
-      <c r="L12" s="24" t="inlineStr">
+      <c r="L12" s="26" t="inlineStr">
         <is>
           <t>RecuperarPasswordModal.tsx</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>HU-04</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>Exploración del Catálogo de Canchas</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>Canchas</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="F13" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="G13" s="13" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="H13" s="25" t="inlineStr">
+      <c r="H13" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="I13" s="16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J13" s="26" t="inlineStr">
+      <c r="J13" s="28" t="inlineStr">
         <is>
           <t>Como cliente, quiero ver las canchas con fotos, tipo (F5, F7, F11), precios por hora y capacidad, para elegir mi cancha.</t>
         </is>
       </c>
-      <c r="K13" s="26" t="inlineStr">
+      <c r="K13" s="28" t="inlineStr">
         <is>
           <t>GET /api/canchas/</t>
         </is>
       </c>
-      <c r="L13" s="26" t="inlineStr">
+      <c r="L13" s="28" t="inlineStr">
         <is>
           <t>Canchas.tsx</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>HU-05</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>Filtrado Rápido por Tipo de Cancha</t>
         </is>
@@ -1456,94 +1464,94 @@
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="H14" s="25" t="inlineStr">
+      <c r="H14" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr">
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J14" s="24" t="inlineStr">
+      <c r="J14" s="26" t="inlineStr">
         <is>
           <t>Como cliente, quiero filtrar las canchas por botones píldora (Todas, F5, F7, F11), para encontrar rápido lo que busco.</t>
         </is>
       </c>
-      <c r="K14" s="24" t="inlineStr">
+      <c r="K14" s="26" t="inlineStr">
         <is>
           <t>GET /api/canchas/?tipo=...</t>
         </is>
       </c>
-      <c r="L14" s="24" t="inlineStr">
+      <c r="L14" s="26" t="inlineStr">
         <is>
           <t>Canchas.tsx</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>HU-06</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>Consulta de Disponibilidad en Tiempo Real</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>Agendamiento</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="F15" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="G15" s="13" t="inlineStr">
+      <c r="G15" s="14" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="H15" s="25" t="inlineStr">
+      <c r="H15" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="I15" s="16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J15" s="26" t="inlineStr">
+      <c r="J15" s="28" t="inlineStr">
         <is>
           <t>Como cliente, quiero seleccionar una fecha en el calendario y ver qué horas están libres vs ocupadas, para planear mi partido.</t>
         </is>
       </c>
-      <c r="K15" s="26" t="inlineStr">
+      <c r="K15" s="28" t="inlineStr">
         <is>
           <t>GET /api/canchas/{id}/disponibilidad</t>
         </is>
       </c>
-      <c r="L15" s="26" t="inlineStr">
+      <c r="L15" s="28" t="inlineStr">
         <is>
           <t>ReservaModal.tsx</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>HU-07</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>Creación y Agendamiento de Reserva</t>
         </is>
@@ -1566,94 +1574,94 @@
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="H16" s="25" t="inlineStr">
+      <c r="H16" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr">
+      <c r="I16" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J16" s="24" t="inlineStr">
+      <c r="J16" s="26" t="inlineStr">
         <is>
           <t>Como cliente autenticado, quiero seleccionar la cancha, fecha y horas, para apartar mi turno sin solapamientos.</t>
         </is>
       </c>
-      <c r="K16" s="24" t="inlineStr">
+      <c r="K16" s="26" t="inlineStr">
         <is>
           <t>POST /api/reservas/</t>
         </is>
       </c>
-      <c r="L16" s="24" t="inlineStr">
+      <c r="L16" s="26" t="inlineStr">
         <is>
           <t>ReservaModal.tsx</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>HU-08</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="C17" s="28" t="inlineStr">
         <is>
           <t>Cálculo Automático de Tarifas</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>Reservas</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="F17" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="G17" s="13" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="H17" s="25" t="inlineStr">
+      <c r="H17" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr">
+      <c r="I17" s="16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J17" s="26" t="inlineStr">
+      <c r="J17" s="28" t="inlineStr">
         <is>
           <t>Como cliente, quiero que el sistema calcule el costo según las horas y precio de la cancha, para saber el valor exacto.</t>
         </is>
       </c>
-      <c r="K17" s="26" t="inlineStr">
+      <c r="K17" s="28" t="inlineStr">
         <is>
           <t>GET /api/canchas/{id}</t>
         </is>
       </c>
-      <c r="L17" s="26" t="inlineStr">
+      <c r="L17" s="28" t="inlineStr">
         <is>
           <t>ReservaModal.tsx</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>HU-09</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="26" t="inlineStr">
         <is>
           <t>Panel 'Mis Reservas' del Cliente</t>
         </is>
@@ -1676,94 +1684,94 @@
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="H18" s="25" t="inlineStr">
+      <c r="H18" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr">
+      <c r="I18" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J18" s="24" t="inlineStr">
+      <c r="J18" s="26" t="inlineStr">
         <is>
           <t>Como cliente, quiero ver la lista de mis partidos reservados con fecha, hora y estado, para llevar el control de mi agenda.</t>
         </is>
       </c>
-      <c r="K18" s="24" t="inlineStr">
+      <c r="K18" s="26" t="inlineStr">
         <is>
           <t>GET /api/reservas/mis-reservas</t>
         </is>
       </c>
-      <c r="L18" s="24" t="inlineStr">
+      <c r="L18" s="26" t="inlineStr">
         <is>
           <t>DashboardCliente.tsx</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>HU-10</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="C19" s="28" t="inlineStr">
         <is>
           <t>Cancelación de Turnos por el Cliente</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>Reservas</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F19" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="G19" s="13" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="H19" s="25" t="inlineStr">
+      <c r="H19" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I19" s="14" t="inlineStr">
+      <c r="I19" s="16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J19" s="26" t="inlineStr">
+      <c r="J19" s="28" t="inlineStr">
         <is>
           <t>Como cliente, quiero cancelar una reserva que no pueda asistir, para liberar el horario a otros jugadores.</t>
         </is>
       </c>
-      <c r="K19" s="26" t="inlineStr">
+      <c r="K19" s="28" t="inlineStr">
         <is>
           <t>DELETE /api/reservas/{id}</t>
         </is>
       </c>
-      <c r="L19" s="26" t="inlineStr">
+      <c r="L19" s="28" t="inlineStr">
         <is>
           <t>DashboardCliente.tsx</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>HU-11</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>Visualización de Torneos Disponibles</t>
         </is>
@@ -1786,94 +1794,94 @@
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="H20" s="25" t="inlineStr">
+      <c r="H20" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr">
+      <c r="I20" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J20" s="24" t="inlineStr">
+      <c r="J20" s="26" t="inlineStr">
         <is>
           <t>Como cliente, quiero ver los torneos de la sede, categorías, fechas y premios, para enterarme de los campeonatos.</t>
         </is>
       </c>
-      <c r="K20" s="24" t="inlineStr">
+      <c r="K20" s="26" t="inlineStr">
         <is>
           <t>GET /api/torneos/</t>
         </is>
       </c>
-      <c r="L20" s="24" t="inlineStr">
+      <c r="L20" s="26" t="inlineStr">
         <is>
           <t>Torneos.tsx</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>HU-12</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C21" s="28" t="inlineStr">
         <is>
           <t>Inscripción de Equipo a Torneos</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>Torneos</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F21" s="13" t="n">
+      <c r="F21" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="G21" s="13" t="inlineStr">
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="H21" s="25" t="inlineStr">
+      <c r="H21" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I21" s="14" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="J21" s="26" t="inlineStr">
+      <c r="I21" s="16" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="28" t="inlineStr">
         <is>
           <t>Como capitán de equipo, quiero inscribir mi equipo en un torneo abierto, para competir por el trofeo y premio.</t>
         </is>
       </c>
-      <c r="K21" s="26" t="inlineStr">
+      <c r="K21" s="28" t="inlineStr">
         <is>
           <t>POST /api/torneos/{id}/inscribir</t>
         </is>
       </c>
-      <c r="L21" s="26" t="inlineStr">
+      <c r="L21" s="28" t="inlineStr">
         <is>
           <t>Torneos.tsx</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>HU-13</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="26" t="inlineStr">
         <is>
           <t>Dock Lateral: Modo Oscuro y Modo Claro</t>
         </is>
@@ -1896,94 +1904,94 @@
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="H22" s="25" t="inlineStr">
+      <c r="H22" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr">
+      <c r="I22" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J22" s="24" t="inlineStr">
+      <c r="J22" s="26" t="inlineStr">
         <is>
           <t>Como usuario, quiero alternar entre tema oscuro y claro desde un botón elegante a la derecha, para cuidar mi vista.</t>
         </is>
       </c>
-      <c r="K22" s="24" t="inlineStr">
+      <c r="K22" s="26" t="inlineStr">
         <is>
           <t>Client-side Theme</t>
         </is>
       </c>
-      <c r="L22" s="24" t="inlineStr">
+      <c r="L22" s="26" t="inlineStr">
         <is>
           <t>ThemeJoystick.tsx</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>HU-14</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
+      <c r="C23" s="28" t="inlineStr">
         <is>
           <t>Dock Lateral: Modo Celular Interactivo</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>UI / UX</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F23" s="13" t="n">
+      <c r="F23" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="G23" s="13" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="H23" s="25" t="inlineStr">
+      <c r="H23" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I23" s="14" t="inlineStr">
+      <c r="I23" s="16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J23" s="26" t="inlineStr">
+      <c r="J23" s="28" t="inlineStr">
         <is>
           <t>Como usuario o evaluador, quiero simular la vista en un marco de smartphone con dynamic island, para probar responsividad.</t>
         </is>
       </c>
-      <c r="K23" s="26" t="inlineStr">
+      <c r="K23" s="28" t="inlineStr">
         <is>
           <t>Client-side Viewport</t>
         </is>
       </c>
-      <c r="L23" s="26" t="inlineStr">
+      <c r="L23" s="28" t="inlineStr">
         <is>
           <t>ThemeJoystick.tsx</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>HU-15</t>
         </is>
       </c>
-      <c r="C24" s="24" t="inlineStr">
+      <c r="C24" s="26" t="inlineStr">
         <is>
           <t>Dock Lateral: Modo Computador (PC)</t>
         </is>
@@ -2006,304 +2014,304 @@
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="H24" s="25" t="inlineStr">
+      <c r="H24" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr">
+      <c r="I24" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J24" s="24" t="inlineStr">
+      <c r="J24" s="26" t="inlineStr">
         <is>
           <t>Como usuario de escritorio, quiero regresar a la vista panorámica de PC con un clic, para ver todo el contenido.</t>
         </is>
       </c>
-      <c r="K24" s="24" t="inlineStr">
+      <c r="K24" s="26" t="inlineStr">
         <is>
           <t>Client-side Viewport</t>
         </is>
       </c>
-      <c r="L24" s="24" t="inlineStr">
+      <c r="L24" s="26" t="inlineStr">
         <is>
           <t>ThemeJoystick.tsx</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>HU-16</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
-        <is>
-          <t>Tablón de Retos y Búsqueda de Rivales</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
-          <t>Comunidad</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="C25" s="28" t="inlineStr">
+        <is>
+          <t>Pasarela de Pagos Online PSE / Wompi</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Pagos</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="H25" s="29" t="inlineStr">
+        <is>
+          <t>En Progreso</t>
+        </is>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J25" s="28" t="inlineStr">
+        <is>
+          <t>Como cliente, quiero pagar mi reserva en línea con tarjeta débito/crédito o PSE en pasarela bancaria en vivo.</t>
+        </is>
+      </c>
+      <c r="K25" s="28" t="inlineStr">
+        <is>
+          <t>Integración Pasarela API</t>
+        </is>
+      </c>
+      <c r="L25" s="28" t="inlineStr">
+        <is>
+          <t>PasarelaPago.tsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>HU-17</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>Descarga de Comprobante PDF con Código QR</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Comprobantes</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="H26" s="29" t="inlineStr">
+        <is>
+          <t>En Progreso</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J26" s="26" t="inlineStr">
+        <is>
+          <t>Como cliente con reserva confirmada, quiero descargar un tiquete en PDF con código QR para mostrar en recepción.</t>
+        </is>
+      </c>
+      <c r="K26" s="26" t="inlineStr">
+        <is>
+          <t>Generador PDF Backend</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="inlineStr">
+        <is>
+          <t>ComprobanteReserva.tsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>HU-18</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="inlineStr">
+        <is>
+          <t>Notificaciones de Recordatorio por SMS / WhatsApp</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>Notificaciones</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="F27" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="G25" s="13" t="inlineStr">
+      <c r="G27" s="14" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="H25" s="25" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-      <c r="I25" s="14" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J25" s="26" t="inlineStr">
-        <is>
-          <t>Como jugador sin equipo completo, quiero publicar retos en el tablón de la sede, para encontrar rivales o jugadores.</t>
-        </is>
-      </c>
-      <c r="K25" s="26" t="inlineStr">
-        <is>
-          <t>Client-side State</t>
-        </is>
-      </c>
-      <c r="L25" s="26" t="inlineStr">
-        <is>
-          <t>TablonRetos.tsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>HU-17</t>
-        </is>
-      </c>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>Galería Acordeón Visual de Canchas</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>UI / UX</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="n">
+      <c r="H27" s="29" t="inlineStr">
+        <is>
+          <t>En Progreso</t>
+        </is>
+      </c>
+      <c r="I27" s="16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J27" s="28" t="inlineStr">
+        <is>
+          <t>Como cliente, quiero recibir un mensaje de recordatorio 2 horas antes de mi partido programado.</t>
+        </is>
+      </c>
+      <c r="K27" s="28" t="inlineStr">
+        <is>
+          <t>Twilio / Meta API</t>
+        </is>
+      </c>
+      <c r="L27" s="28" t="inlineStr">
+        <is>
+          <t>ServicioRecordatorios.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>HU-19</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>Sistema de Puntos y Fidelización de Jugadores</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Fidelización</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="H28" s="29" t="inlineStr">
+        <is>
+          <t>En Progreso</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J28" s="26" t="inlineStr">
+        <is>
+          <t>Como cliente frecuente, quiero acumular puntos por cada hora jugada para canjear por horas gratis.</t>
+        </is>
+      </c>
+      <c r="K28" s="26" t="inlineStr">
+        <is>
+          <t>Módulo Puntos DB</t>
+        </is>
+      </c>
+      <c r="L28" s="26" t="inlineStr">
+        <is>
+          <t>PuntosCliente.tsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>HU-20</t>
+        </is>
+      </c>
+      <c r="C29" s="28" t="inlineStr">
+        <is>
+          <t>Sincronización con Google Calendar</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>Integraciones</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="G29" s="14" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="H26" s="25" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-      <c r="I26" s="11" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J26" s="24" t="inlineStr">
-        <is>
-          <t>Como cliente, quiero ver imágenes dinámicas con iluminación LED y césped sintético, para motivarme a reservar.</t>
-        </is>
-      </c>
-      <c r="K26" s="24" t="inlineStr">
-        <is>
-          <t>Client-side Showcase</t>
-        </is>
-      </c>
-      <c r="L26" s="24" t="inlineStr">
-        <is>
-          <t>AcordeonCanchas.tsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>HU-18</t>
-        </is>
-      </c>
-      <c r="C27" s="26" t="inlineStr">
-        <is>
-          <t>Calificaciones y Reseñas con Estrellas</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>Reseñas</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F27" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="G27" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="H27" s="25" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-      <c r="I27" s="14" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="26" t="inlineStr">
-        <is>
-          <t>Como cliente, quiero calificar las canchas con estrellas (1-5) y comentarios, para recomendar la sede.</t>
-        </is>
-      </c>
-      <c r="K27" s="26" t="inlineStr">
-        <is>
-          <t>GET/POST /api/resenas/</t>
-        </is>
-      </c>
-      <c r="L27" s="26" t="inlineStr">
-        <is>
-          <t>ResenasModal.tsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>HU-19</t>
-        </is>
-      </c>
-      <c r="C28" s="24" t="inlineStr">
-        <is>
-          <t>Contacto Inmediato vía WhatsApp</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>Soporte</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="H28" s="25" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="24" t="inlineStr">
-        <is>
-          <t>Como cliente, quiero un botón para escribir directo al WhatsApp de la sede, para resolver dudas rápidas.</t>
-        </is>
-      </c>
-      <c r="K28" s="24" t="inlineStr">
-        <is>
-          <t>WhatsApp API Link</t>
-        </is>
-      </c>
-      <c r="L28" s="24" t="inlineStr">
-        <is>
-          <t>AcordeonCanchas.tsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>HU-20</t>
-        </is>
-      </c>
-      <c r="C29" s="26" t="inlineStr">
-        <is>
-          <t>Barra de Fortaleza de Contraseña</t>
-        </is>
-      </c>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
-          <t>Seguridad</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F29" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G29" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 1</t>
-        </is>
-      </c>
-      <c r="H29" s="25" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-      <c r="I29" s="14" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J29" s="26" t="inlineStr">
-        <is>
-          <t>Como usuario al crear o cambiar clave, quiero ver un indicador visual de qué tan segura es mi contraseña.</t>
-        </is>
-      </c>
-      <c r="K29" s="26" t="inlineStr">
-        <is>
-          <t>Client-side Validator</t>
-        </is>
-      </c>
-      <c r="L29" s="26" t="inlineStr">
-        <is>
-          <t>RecuperarPasswordModal.tsx</t>
+      <c r="H29" s="29" t="inlineStr">
+        <is>
+          <t>En Progreso</t>
+        </is>
+      </c>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J29" s="28" t="inlineStr">
+        <is>
+          <t>Como cliente, quiero un botón para añadir automáticamente el partido agendado a mi calendario de Google.</t>
+        </is>
+      </c>
+      <c r="K29" s="28" t="inlineStr">
+        <is>
+          <t>Google Calendar API</t>
+        </is>
+      </c>
+      <c r="L29" s="28" t="inlineStr">
+        <is>
+          <t>BotonCalendar.tsx</t>
         </is>
       </c>
     </row>
@@ -2322,16 +2330,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="48" customWidth="1" min="10" max="10"/>
     <col width="33" customWidth="1" min="11" max="11"/>
@@ -2340,47 +2348,47 @@
   <sheetData>
     <row r="1"/>
     <row r="2">
-      <c r="B2" s="27" t="inlineStr">
-        <is>
-          <t>👑 HISTORIAS DE USUARIO — MÓDULO ADMINISTRADOR &amp; GESTIÓN</t>
+      <c r="B2" s="30" t="inlineStr">
+        <is>
+          <t>👑 HISTORIAS DE USUARIO — MÓDULO ADMINISTRADOR &amp; GESTIÓN (77% AVANCE)</t>
         </is>
       </c>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>Total HUs Admin:</t>
         </is>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="23">
         <f>COUNTA(B10:B27)</f>
         <v/>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="22" t="inlineStr">
         <is>
           <t>Completadas:</t>
         </is>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="23">
         <f>COUNTIF(H10:H27, "Completado")</f>
         <v/>
       </c>
-      <c r="F4" s="20" t="inlineStr">
+      <c r="F4" s="22" t="inlineStr">
         <is>
           <t>% Avance Admin:</t>
         </is>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="24">
         <f>E4/C4</f>
         <v/>
       </c>
-      <c r="H4" s="20" t="inlineStr">
+      <c r="H4" s="22" t="inlineStr">
         <is>
           <t>Puntos Totales:</t>
         </is>
       </c>
-      <c r="I4" s="21">
+      <c r="I4" s="23">
         <f>SUM(F10:F27)</f>
         <v/>
       </c>
@@ -2390,69 +2398,69 @@
     <row r="7"/>
     <row r="8"/>
     <row r="9">
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
         <is>
           <t>Título de la Historia</t>
         </is>
       </c>
-      <c r="D9" s="28" t="inlineStr">
+      <c r="D9" s="31" t="inlineStr">
         <is>
           <t>Módulo</t>
         </is>
       </c>
-      <c r="E9" s="28" t="inlineStr">
+      <c r="E9" s="31" t="inlineStr">
         <is>
           <t>Prioridad</t>
         </is>
       </c>
-      <c r="F9" s="28" t="inlineStr">
+      <c r="F9" s="31" t="inlineStr">
         <is>
           <t>Puntos</t>
         </is>
       </c>
-      <c r="G9" s="28" t="inlineStr">
+      <c r="G9" s="31" t="inlineStr">
         <is>
           <t>Sprint</t>
         </is>
       </c>
-      <c r="H9" s="28" t="inlineStr">
+      <c r="H9" s="31" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="I9" s="28" t="inlineStr">
+      <c r="I9" s="31" t="inlineStr">
         <is>
           <t>% Avance</t>
         </is>
       </c>
-      <c r="J9" s="28" t="inlineStr">
+      <c r="J9" s="31" t="inlineStr">
         <is>
           <t>Descripción (Como / Quiero / Para)</t>
         </is>
       </c>
-      <c r="K9" s="28" t="inlineStr">
+      <c r="K9" s="31" t="inlineStr">
         <is>
           <t>Endpoint API Backend</t>
         </is>
       </c>
-      <c r="L9" s="28" t="inlineStr">
+      <c r="L9" s="31" t="inlineStr">
         <is>
           <t>Componente Frontend</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>HU-21</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>Panel de Control Principal (Dashboard Admin)</t>
         </is>
@@ -2475,94 +2483,94 @@
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="H10" s="25" t="inlineStr">
+      <c r="H10" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J10" s="24" t="inlineStr">
+      <c r="J10" s="26" t="inlineStr">
         <is>
           <t>Como administrador, quiero ver el resumen global de reservas, ingresos totales, usuarios y canchas activas en un panel.</t>
         </is>
       </c>
-      <c r="K10" s="24" t="inlineStr">
+      <c r="K10" s="26" t="inlineStr">
         <is>
           <t>GET /api/reportes/resumen</t>
         </is>
       </c>
-      <c r="L10" s="24" t="inlineStr">
+      <c r="L10" s="26" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>HU-22</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>Métricas Financieras e Ingresos en Tiempo Real</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>Reportes</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="G11" s="13" t="inlineStr">
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="H11" s="25" t="inlineStr">
+      <c r="H11" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I11" s="16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J11" s="26" t="inlineStr">
+      <c r="J11" s="28" t="inlineStr">
         <is>
           <t>Como administrador, quiero consultar el dinero recaudado en el mes y proyecciones, para evaluar la rentabilidad.</t>
         </is>
       </c>
-      <c r="K11" s="26" t="inlineStr">
+      <c r="K11" s="28" t="inlineStr">
         <is>
           <t>GET /api/reportes/resumen</t>
         </is>
       </c>
-      <c r="L11" s="26" t="inlineStr">
+      <c r="L11" s="28" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>HU-23</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>Exportación de Reportes a Excel (.xlsx / .csv)</t>
         </is>
@@ -2585,94 +2593,94 @@
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="H12" s="25" t="inlineStr">
+      <c r="H12" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J12" s="24" t="inlineStr">
+      <c r="J12" s="26" t="inlineStr">
         <is>
           <t>Como administrador, quiero descargar la base de datos de reservas e ingresos en formato Excel, para contabilidad física.</t>
         </is>
       </c>
-      <c r="K12" s="24" t="inlineStr">
+      <c r="K12" s="26" t="inlineStr">
         <is>
           <t>Client Export / API</t>
         </is>
       </c>
-      <c r="L12" s="24" t="inlineStr">
+      <c r="L12" s="26" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>HU-24</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>Creación y Registro de Nuevas Canchas</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>Canchas</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="F13" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="G13" s="13" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="H13" s="25" t="inlineStr">
+      <c r="H13" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="I13" s="16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J13" s="26" t="inlineStr">
+      <c r="J13" s="28" t="inlineStr">
         <is>
           <t>Como administrador, quiero agregar nuevas canchas con su tipo, capacidad, precio/hora y servicios, para ampliar la oferta.</t>
         </is>
       </c>
-      <c r="K13" s="26" t="inlineStr">
+      <c r="K13" s="28" t="inlineStr">
         <is>
           <t>POST /api/canchas/</t>
         </is>
       </c>
-      <c r="L13" s="26" t="inlineStr">
+      <c r="L13" s="28" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>HU-25</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>Edición y Actualización de Tarifas de Canchas</t>
         </is>
@@ -2695,94 +2703,94 @@
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="H14" s="25" t="inlineStr">
+      <c r="H14" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr">
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J14" s="24" t="inlineStr">
+      <c r="J14" s="26" t="inlineStr">
         <is>
           <t>Como administrador, quiero modificar los precios por hora y características de cada cancha, para ajustar promociones.</t>
         </is>
       </c>
-      <c r="K14" s="24" t="inlineStr">
+      <c r="K14" s="26" t="inlineStr">
         <is>
           <t>PUT /api/canchas/{id}</t>
         </is>
       </c>
-      <c r="L14" s="24" t="inlineStr">
+      <c r="L14" s="26" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>HU-26</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>Desactivación / Mantenimiento de Canchas</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>Canchas</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="F15" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="G15" s="13" t="inlineStr">
+      <c r="G15" s="14" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="H15" s="25" t="inlineStr">
+      <c r="H15" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="I15" s="16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J15" s="26" t="inlineStr">
+      <c r="J15" s="28" t="inlineStr">
         <is>
           <t>Como administrador, quiero deshabilitar temporalmente una cancha en mantenimiento, para que los clientes no la reserven.</t>
         </is>
       </c>
-      <c r="K15" s="26" t="inlineStr">
+      <c r="K15" s="28" t="inlineStr">
         <is>
           <t>PUT /api/canchas/{id}</t>
         </is>
       </c>
-      <c r="L15" s="26" t="inlineStr">
+      <c r="L15" s="28" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>HU-27</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>Eliminación Segura de Canchas</t>
         </is>
@@ -2805,94 +2813,94 @@
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="H16" s="25" t="inlineStr">
+      <c r="H16" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr">
+      <c r="I16" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J16" s="24" t="inlineStr">
+      <c r="J16" s="26" t="inlineStr">
         <is>
           <t>Como administrador, quiero dar de baja canchas obsoletas con confirmación de seguridad.</t>
         </is>
       </c>
-      <c r="K16" s="24" t="inlineStr">
+      <c r="K16" s="26" t="inlineStr">
         <is>
           <t>DELETE /api/canchas/{id}</t>
         </is>
       </c>
-      <c r="L16" s="24" t="inlineStr">
+      <c r="L16" s="26" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>HU-28</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="C17" s="28" t="inlineStr">
         <is>
           <t>Gestión Completa de Reservas Globales</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>Reservas</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="F17" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="G17" s="13" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="H17" s="25" t="inlineStr">
+      <c r="H17" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr">
+      <c r="I17" s="16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J17" s="26" t="inlineStr">
+      <c r="J17" s="28" t="inlineStr">
         <is>
           <t>Como administrador, quiero ver la lista de todas las reservas de todos los clientes con filtros por fecha y cancha.</t>
         </is>
       </c>
-      <c r="K17" s="26" t="inlineStr">
+      <c r="K17" s="28" t="inlineStr">
         <is>
           <t>GET /api/reservas/</t>
         </is>
       </c>
-      <c r="L17" s="26" t="inlineStr">
+      <c r="L17" s="28" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>HU-29</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="26" t="inlineStr">
         <is>
           <t>Cambio de Estado de Reserva (Confirmar / Completar)</t>
         </is>
@@ -2915,94 +2923,94 @@
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="H18" s="25" t="inlineStr">
+      <c r="H18" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr">
+      <c r="I18" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J18" s="24" t="inlineStr">
+      <c r="J18" s="26" t="inlineStr">
         <is>
           <t>Como administrador, quiero marcar reservas como pagadas, completadas o canceladas al llegar los jugadores a la sede.</t>
         </is>
       </c>
-      <c r="K18" s="24" t="inlineStr">
+      <c r="K18" s="26" t="inlineStr">
         <is>
           <t>PUT /api/reservas/{id}/estado</t>
         </is>
       </c>
-      <c r="L18" s="24" t="inlineStr">
+      <c r="L18" s="26" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>HU-30</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="C19" s="28" t="inlineStr">
         <is>
           <t>Registro y Alta de Empleados de la Sede</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F19" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="G19" s="13" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="H19" s="25" t="inlineStr">
+      <c r="H19" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I19" s="14" t="inlineStr">
+      <c r="I19" s="16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J19" s="26" t="inlineStr">
+      <c r="J19" s="28" t="inlineStr">
         <is>
           <t>Como administrador, quiero registrar empleados (Coordinadores, Mantenimiento, Seguridad, Atención), para ordenar el personal.</t>
         </is>
       </c>
-      <c r="K19" s="26" t="inlineStr">
+      <c r="K19" s="28" t="inlineStr">
         <is>
           <t>POST /api/empleados/</t>
         </is>
       </c>
-      <c r="L19" s="26" t="inlineStr">
+      <c r="L19" s="28" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>HU-31</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>Listado y Edición del Personal</t>
         </is>
@@ -3025,94 +3033,94 @@
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="H20" s="25" t="inlineStr">
+      <c r="H20" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr">
+      <c r="I20" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J20" s="24" t="inlineStr">
+      <c r="J20" s="26" t="inlineStr">
         <is>
           <t>Como administrador, quiero consultar el teléfono, correo y cargo de cada empleado y editar sus datos.</t>
         </is>
       </c>
-      <c r="K20" s="24" t="inlineStr">
+      <c r="K20" s="26" t="inlineStr">
         <is>
           <t>GET/PUT /api/empleados/</t>
         </is>
       </c>
-      <c r="L20" s="24" t="inlineStr">
+      <c r="L20" s="26" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>HU-32</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C21" s="28" t="inlineStr">
         <is>
           <t>Activación y Desactivación de Empleados</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F21" s="13" t="n">
+      <c r="F21" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="G21" s="13" t="inlineStr">
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="H21" s="25" t="inlineStr">
+      <c r="H21" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I21" s="14" t="inlineStr">
+      <c r="I21" s="16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J21" s="26" t="inlineStr">
+      <c r="J21" s="28" t="inlineStr">
         <is>
           <t>Como administrador, quiero desactivar empleados inactivos sin perder el registro histórico.</t>
         </is>
       </c>
-      <c r="K21" s="26" t="inlineStr">
+      <c r="K21" s="28" t="inlineStr">
         <is>
           <t>PUT /api/empleados/{id}</t>
         </is>
       </c>
-      <c r="L21" s="26" t="inlineStr">
+      <c r="L21" s="28" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>HU-33</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="26" t="inlineStr">
         <is>
           <t>Creación y Apertura de Nuevos Torneos</t>
         </is>
@@ -3135,101 +3143,101 @@
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="H22" s="25" t="inlineStr">
+      <c r="H22" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr">
+      <c r="I22" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J22" s="24" t="inlineStr">
+      <c r="J22" s="26" t="inlineStr">
         <is>
           <t>Como administrador, quiero crear torneos definiendo cancha sede, fechas, premio garantizado, valor y cupo máximo.</t>
         </is>
       </c>
-      <c r="K22" s="24" t="inlineStr">
+      <c r="K22" s="26" t="inlineStr">
         <is>
           <t>POST /api/torneos/</t>
         </is>
       </c>
-      <c r="L22" s="24" t="inlineStr">
+      <c r="L22" s="26" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>HU-34</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
-        <is>
-          <t>Cierre y Finalización de Torneos</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="C23" s="28" t="inlineStr">
+        <is>
+          <t>Control de Acceso y Protección de Rutas RBAC</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H23" s="27" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="28" t="inlineStr">
+        <is>
+          <t>Como sistema, quiero bloquear el acceso al panel administrativo a usuarios no autenticados o con rol cliente (403 Forbidden).</t>
+        </is>
+      </c>
+      <c r="K23" s="28" t="inlineStr">
+        <is>
+          <t>Middleware Auth JWT</t>
+        </is>
+      </c>
+      <c r="L23" s="28" t="inlineStr">
+        <is>
+          <t>DashboardAdmin.tsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>HU-35</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Generador Automático de Cuadro de Llaves (Brackets)</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>Torneos</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G23" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="H23" s="25" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-      <c r="I23" s="14" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="J23" s="26" t="inlineStr">
-        <is>
-          <t>Como administrador, quiero cambiar el estado de torneos de 'abierto' a 'en curso' o 'finalizado'.</t>
-        </is>
-      </c>
-      <c r="K23" s="26" t="inlineStr">
-        <is>
-          <t>PUT /api/torneos/{id}</t>
-        </is>
-      </c>
-      <c r="L23" s="26" t="inlineStr">
-        <is>
-          <t>DashboardAdmin.tsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>HU-35</t>
-        </is>
-      </c>
-      <c r="C24" s="24" t="inlineStr">
-        <is>
-          <t>Directorio de Clientes Registrados</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>Usuarios</t>
         </is>
       </c>
       <c r="E24" s="10" t="inlineStr">
@@ -3242,104 +3250,104 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
-        </is>
-      </c>
-      <c r="H24" s="25" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-      <c r="I24" s="11" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="24" t="inlineStr">
-        <is>
-          <t>Como administrador, quiero ver el listado de todos los clientes registrados, sus correos y teléfonos de contacto.</t>
-        </is>
-      </c>
-      <c r="K24" s="24" t="inlineStr">
-        <is>
-          <t>GET /api/usuarios/clientes</t>
-        </is>
-      </c>
-      <c r="L24" s="24" t="inlineStr">
-        <is>
-          <t>DashboardAdmin.tsx</t>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="H24" s="29" t="inlineStr">
+        <is>
+          <t>En Progreso</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J24" s="26" t="inlineStr">
+        <is>
+          <t>Como administrador, quiero que el sistema sortee y arme el cuadro de octavos y cuartos de final automáticamente.</t>
+        </is>
+      </c>
+      <c r="K24" s="26" t="inlineStr">
+        <is>
+          <t>Algoritmo Torneos</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="inlineStr">
+        <is>
+          <t>BracketsTorneo.tsx</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>HU-36</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
-        <is>
-          <t>Control de Acceso y Protección de Rutas RBAC</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="C25" s="28" t="inlineStr">
+        <is>
+          <t>Lector y Validador de Códigos QR en Portería</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>Seguridad</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="n">
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="G25" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 1</t>
-        </is>
-      </c>
-      <c r="H25" s="25" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-      <c r="I25" s="14" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J25" s="26" t="inlineStr">
-        <is>
-          <t>Como sistema, quiero bloquear el acceso al panel administrativo a usuarios no autenticados o con rol cliente (403 Forbidden).</t>
-        </is>
-      </c>
-      <c r="K25" s="26" t="inlineStr">
-        <is>
-          <t>Middleware Auth JWT</t>
-        </is>
-      </c>
-      <c r="L25" s="26" t="inlineStr">
-        <is>
-          <t>DashboardAdmin.tsx</t>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="H25" s="29" t="inlineStr">
+        <is>
+          <t>En Progreso</t>
+        </is>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J25" s="28" t="inlineStr">
+        <is>
+          <t>Como recepcionista o portero, quiero escanear el QR del tiquete del cliente para validar el ingreso a la cancha.</t>
+        </is>
+      </c>
+      <c r="K25" s="28" t="inlineStr">
+        <is>
+          <t>Escáner Cámara Web</t>
+        </is>
+      </c>
+      <c r="L25" s="28" t="inlineStr">
+        <is>
+          <t>ValidadorQR.tsx</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>HU-37</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>Base de Datos SQLite Nativa con Claves Foráneas</t>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>Despliegue Continuo en Servidores Cloud (CI/CD)</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
@@ -3352,87 +3360,87 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Sprint 1</t>
-        </is>
-      </c>
-      <c r="H26" s="25" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-      <c r="I26" s="11" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J26" s="24" t="inlineStr">
-        <is>
-          <t>Como desarrollador, quiero una base de datos local SQLite con relaciones íntegras y soporte MySQL opcional, para portabilidad total.</t>
-        </is>
-      </c>
-      <c r="K26" s="24" t="inlineStr">
-        <is>
-          <t>SQLAlchemy ORM PRAGMA</t>
-        </is>
-      </c>
-      <c r="L26" s="24" t="inlineStr">
-        <is>
-          <t>database.py</t>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="H26" s="29" t="inlineStr">
+        <is>
+          <t>En Progreso</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J26" s="26" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero configurar pipelines de CI/CD para despliegue automático en la nube con dominio .com.</t>
+        </is>
+      </c>
+      <c r="K26" s="26" t="inlineStr">
+        <is>
+          <t>GitHub Actions / Docker</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="inlineStr">
+        <is>
+          <t>Dockerfile</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>HU-38</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
-        <is>
-          <t>Configuración SMTP Gmail para Notificaciones</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="F27" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="G27" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 1</t>
-        </is>
-      </c>
-      <c r="H27" s="25" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-      <c r="I27" s="14" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="26" t="inlineStr">
-        <is>
-          <t>Como desarrollador, quiero un servicio de correo con servidor Gmail SMTP TLS 587, para despachar correos a bandejas reales.</t>
-        </is>
-      </c>
-      <c r="K27" s="26" t="inlineStr">
-        <is>
-          <t>smtplib + MIME HTML</t>
-        </is>
-      </c>
-      <c r="L27" s="26" t="inlineStr">
-        <is>
-          <t>email_service.py</t>
+      <c r="C27" s="28" t="inlineStr">
+        <is>
+          <t>Módulo de Auditoría y Registro de Logs de Cambios</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="H27" s="29" t="inlineStr">
+        <is>
+          <t>En Progreso</t>
+        </is>
+      </c>
+      <c r="I27" s="16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="J27" s="28" t="inlineStr">
+        <is>
+          <t>Como administrador general, quiero ver qué empleado modificó una tarifa o canceló una reserva con fecha y hora.</t>
+        </is>
+      </c>
+      <c r="K27" s="28" t="inlineStr">
+        <is>
+          <t>Tabla Auditoria DB</t>
+        </is>
+      </c>
+      <c r="L27" s="28" t="inlineStr">
+        <is>
+          <t>LogsAuditoria.tsx</t>
         </is>
       </c>
     </row>
@@ -3451,17 +3459,17 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M47"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="48" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="48" customWidth="1" min="11" max="11"/>
     <col width="40" customWidth="1" min="12" max="12"/>
@@ -3470,47 +3478,47 @@
   <sheetData>
     <row r="1"/>
     <row r="2">
-      <c r="B2" s="29" t="inlineStr">
-        <is>
-          <t>📋 MATRIZ GENERAL DE HISTORIAS DE USUARIO — FUTBOLZONE (SENA ADSO III)</t>
+      <c r="B2" s="32" t="inlineStr">
+        <is>
+          <t>📋 MATRIZ GENERAL DE HISTORIAS DE USUARIO — AVANCE 75.0% (SENA ADSO III)</t>
         </is>
       </c>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>Total HUs:</t>
         </is>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="23">
         <f>COUNTA(B10:B47)</f>
         <v/>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="22" t="inlineStr">
         <is>
           <t>% Avance Global:</t>
         </is>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="24">
         <f>COUNTIF(I10:I47, "Completado")/C4</f>
         <v/>
       </c>
-      <c r="F4" s="20" t="inlineStr">
+      <c r="F4" s="22" t="inlineStr">
         <is>
           <t>Puntos Totales:</t>
         </is>
       </c>
-      <c r="G4" s="21">
+      <c r="G4" s="23">
         <f>SUM(G10:G47)</f>
         <v/>
       </c>
-      <c r="H4" s="20" t="inlineStr">
+      <c r="H4" s="22" t="inlineStr">
         <is>
           <t>Puntos Listos:</t>
         </is>
       </c>
-      <c r="I4" s="21">
+      <c r="I4" s="23">
         <f>SUMIF(I10:I47, "Completado", G10:G47)</f>
         <v/>
       </c>
@@ -3582,17 +3590,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>HU-01</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>Registro de Cuenta de Cliente</t>
         </is>
       </c>
-      <c r="D10" s="30" t="inlineStr">
+      <c r="D10" s="33" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
@@ -3615,104 +3623,104 @@
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="I10" s="25" t="inlineStr">
+      <c r="I10" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K10" s="24" t="inlineStr">
+      <c r="K10" s="26" t="inlineStr">
         <is>
           <t>Como visitante, quiero registrar mis datos con nombre, correo y clave, para tener una cuenta y reservar canchas.</t>
         </is>
       </c>
-      <c r="L10" s="24" t="inlineStr">
+      <c r="L10" s="26" t="inlineStr">
         <is>
           <t>POST /api/usuarios/registro</t>
         </is>
       </c>
-      <c r="M10" s="24" t="inlineStr">
+      <c r="M10" s="26" t="inlineStr">
         <is>
           <t>LoginModal.tsx</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>HU-02</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>Inicio de Sesión con JWT</t>
         </is>
       </c>
-      <c r="D11" s="31" t="inlineStr">
+      <c r="D11" s="34" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>Seguridad</t>
         </is>
       </c>
-      <c r="F11" s="13" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="G11" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H11" s="13" t="inlineStr">
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="I11" s="25" t="inlineStr">
+      <c r="I11" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J11" s="14" t="inlineStr">
+      <c r="J11" s="16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K11" s="26" t="inlineStr">
+      <c r="K11" s="28" t="inlineStr">
         <is>
           <t>Como cliente, quiero iniciar sesión con mi correo y contraseña, para acceder a mis reservas y perfil.</t>
         </is>
       </c>
-      <c r="L11" s="26" t="inlineStr">
+      <c r="L11" s="28" t="inlineStr">
         <is>
           <t>POST /api/usuarios/login</t>
         </is>
       </c>
-      <c r="M11" s="26" t="inlineStr">
+      <c r="M11" s="28" t="inlineStr">
         <is>
           <t>LoginModal.tsx</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>HU-03</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>Recuperación de Contraseña con PIN Gmail</t>
         </is>
       </c>
-      <c r="D12" s="30" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
@@ -3735,104 +3743,104 @@
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="I12" s="25" t="inlineStr">
+      <c r="I12" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J12" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K12" s="24" t="inlineStr">
+      <c r="K12" s="26" t="inlineStr">
         <is>
           <t>Como cliente que olvidó su clave, quiero recibir un PIN de 6 dígitos en mi Gmail real, para restablecer mi acceso.</t>
         </is>
       </c>
-      <c r="L12" s="24" t="inlineStr">
+      <c r="L12" s="26" t="inlineStr">
         <is>
           <t>POST /api/auth/recuperar-password/*</t>
         </is>
       </c>
-      <c r="M12" s="24" t="inlineStr">
+      <c r="M12" s="26" t="inlineStr">
         <is>
           <t>RecuperarPasswordModal.tsx</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>HU-04</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>Exploración del Catálogo de Canchas</t>
         </is>
       </c>
-      <c r="D13" s="31" t="inlineStr">
+      <c r="D13" s="34" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>Canchas</t>
         </is>
       </c>
-      <c r="F13" s="13" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="G13" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="13" t="inlineStr">
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="I13" s="25" t="inlineStr">
+      <c r="I13" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J13" s="14" t="inlineStr">
+      <c r="J13" s="16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K13" s="26" t="inlineStr">
+      <c r="K13" s="28" t="inlineStr">
         <is>
           <t>Como cliente, quiero ver las canchas con fotos, tipo (F5, F7, F11), precios por hora y capacidad, para elegir mi cancha.</t>
         </is>
       </c>
-      <c r="L13" s="26" t="inlineStr">
+      <c r="L13" s="28" t="inlineStr">
         <is>
           <t>GET /api/canchas/</t>
         </is>
       </c>
-      <c r="M13" s="26" t="inlineStr">
+      <c r="M13" s="28" t="inlineStr">
         <is>
           <t>Canchas.tsx</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>HU-05</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>Filtrado Rápido por Tipo de Cancha</t>
         </is>
       </c>
-      <c r="D14" s="30" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
@@ -3855,104 +3863,104 @@
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="I14" s="25" t="inlineStr">
+      <c r="I14" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K14" s="24" t="inlineStr">
+      <c r="K14" s="26" t="inlineStr">
         <is>
           <t>Como cliente, quiero filtrar las canchas por botones píldora (Todas, F5, F7, F11), para encontrar rápido lo que busco.</t>
         </is>
       </c>
-      <c r="L14" s="24" t="inlineStr">
+      <c r="L14" s="26" t="inlineStr">
         <is>
           <t>GET /api/canchas/?tipo=...</t>
         </is>
       </c>
-      <c r="M14" s="24" t="inlineStr">
+      <c r="M14" s="26" t="inlineStr">
         <is>
           <t>Canchas.tsx</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>HU-06</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>Consulta de Disponibilidad en Tiempo Real</t>
         </is>
       </c>
-      <c r="D15" s="31" t="inlineStr">
+      <c r="D15" s="34" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>Agendamiento</t>
         </is>
       </c>
-      <c r="F15" s="13" t="inlineStr">
+      <c r="F15" s="14" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="G15" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H15" s="13" t="inlineStr">
+      <c r="H15" s="14" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="I15" s="25" t="inlineStr">
+      <c r="I15" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J15" s="14" t="inlineStr">
+      <c r="J15" s="16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K15" s="26" t="inlineStr">
+      <c r="K15" s="28" t="inlineStr">
         <is>
           <t>Como cliente, quiero seleccionar una fecha en el calendario y ver qué horas están libres vs ocupadas, para planear mi partido.</t>
         </is>
       </c>
-      <c r="L15" s="26" t="inlineStr">
+      <c r="L15" s="28" t="inlineStr">
         <is>
           <t>GET /api/canchas/{id}/disponibilidad</t>
         </is>
       </c>
-      <c r="M15" s="26" t="inlineStr">
+      <c r="M15" s="28" t="inlineStr">
         <is>
           <t>ReservaModal.tsx</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>HU-07</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>Creación y Agendamiento de Reserva</t>
         </is>
       </c>
-      <c r="D16" s="30" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
@@ -3975,104 +3983,104 @@
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="I16" s="25" t="inlineStr">
+      <c r="I16" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="J16" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K16" s="24" t="inlineStr">
+      <c r="K16" s="26" t="inlineStr">
         <is>
           <t>Como cliente autenticado, quiero seleccionar la cancha, fecha y horas, para apartar mi turno sin solapamientos.</t>
         </is>
       </c>
-      <c r="L16" s="24" t="inlineStr">
+      <c r="L16" s="26" t="inlineStr">
         <is>
           <t>POST /api/reservas/</t>
         </is>
       </c>
-      <c r="M16" s="24" t="inlineStr">
+      <c r="M16" s="26" t="inlineStr">
         <is>
           <t>ReservaModal.tsx</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>HU-08</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="C17" s="28" t="inlineStr">
         <is>
           <t>Cálculo Automático de Tarifas</t>
         </is>
       </c>
-      <c r="D17" s="31" t="inlineStr">
+      <c r="D17" s="34" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>Reservas</t>
         </is>
       </c>
-      <c r="F17" s="13" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="G17" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="H17" s="13" t="inlineStr">
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="I17" s="25" t="inlineStr">
+      <c r="I17" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J17" s="14" t="inlineStr">
+      <c r="J17" s="16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K17" s="26" t="inlineStr">
+      <c r="K17" s="28" t="inlineStr">
         <is>
           <t>Como cliente, quiero que el sistema calcule el costo según las horas y precio de la cancha, para saber el valor exacto.</t>
         </is>
       </c>
-      <c r="L17" s="26" t="inlineStr">
+      <c r="L17" s="28" t="inlineStr">
         <is>
           <t>GET /api/canchas/{id}</t>
         </is>
       </c>
-      <c r="M17" s="26" t="inlineStr">
+      <c r="M17" s="28" t="inlineStr">
         <is>
           <t>ReservaModal.tsx</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>HU-09</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C18" s="26" t="inlineStr">
         <is>
           <t>Panel 'Mis Reservas' del Cliente</t>
         </is>
       </c>
-      <c r="D18" s="30" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
@@ -4095,104 +4103,104 @@
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="I18" s="25" t="inlineStr">
+      <c r="I18" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="J18" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K18" s="24" t="inlineStr">
+      <c r="K18" s="26" t="inlineStr">
         <is>
           <t>Como cliente, quiero ver la lista de mis partidos reservados con fecha, hora y estado, para llevar el control de mi agenda.</t>
         </is>
       </c>
-      <c r="L18" s="24" t="inlineStr">
+      <c r="L18" s="26" t="inlineStr">
         <is>
           <t>GET /api/reservas/mis-reservas</t>
         </is>
       </c>
-      <c r="M18" s="24" t="inlineStr">
+      <c r="M18" s="26" t="inlineStr">
         <is>
           <t>DashboardCliente.tsx</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>HU-10</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="C19" s="28" t="inlineStr">
         <is>
           <t>Cancelación de Turnos por el Cliente</t>
         </is>
       </c>
-      <c r="D19" s="31" t="inlineStr">
+      <c r="D19" s="34" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>Reservas</t>
         </is>
       </c>
-      <c r="F19" s="13" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="G19" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H19" s="13" t="inlineStr">
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="I19" s="25" t="inlineStr">
+      <c r="I19" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J19" s="14" t="inlineStr">
+      <c r="J19" s="16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K19" s="26" t="inlineStr">
+      <c r="K19" s="28" t="inlineStr">
         <is>
           <t>Como cliente, quiero cancelar una reserva que no pueda asistir, para liberar el horario a otros jugadores.</t>
         </is>
       </c>
-      <c r="L19" s="26" t="inlineStr">
+      <c r="L19" s="28" t="inlineStr">
         <is>
           <t>DELETE /api/reservas/{id}</t>
         </is>
       </c>
-      <c r="M19" s="26" t="inlineStr">
+      <c r="M19" s="28" t="inlineStr">
         <is>
           <t>DashboardCliente.tsx</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>HU-11</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>Visualización de Torneos Disponibles</t>
         </is>
       </c>
-      <c r="D20" s="30" t="inlineStr">
+      <c r="D20" s="33" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
@@ -4215,104 +4223,104 @@
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="I20" s="25" t="inlineStr">
+      <c r="I20" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="J20" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K20" s="24" t="inlineStr">
+      <c r="K20" s="26" t="inlineStr">
         <is>
           <t>Como cliente, quiero ver los torneos de la sede, categorías, fechas y premios, para enterarme de los campeonatos.</t>
         </is>
       </c>
-      <c r="L20" s="24" t="inlineStr">
+      <c r="L20" s="26" t="inlineStr">
         <is>
           <t>GET /api/torneos/</t>
         </is>
       </c>
-      <c r="M20" s="24" t="inlineStr">
+      <c r="M20" s="26" t="inlineStr">
         <is>
           <t>Torneos.tsx</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>HU-12</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C21" s="28" t="inlineStr">
         <is>
           <t>Inscripción de Equipo a Torneos</t>
         </is>
       </c>
-      <c r="D21" s="31" t="inlineStr">
+      <c r="D21" s="34" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>Torneos</t>
         </is>
       </c>
-      <c r="F21" s="13" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="G21" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H21" s="13" t="inlineStr">
+      <c r="H21" s="14" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="I21" s="25" t="inlineStr">
+      <c r="I21" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J21" s="14" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="K21" s="26" t="inlineStr">
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K21" s="28" t="inlineStr">
         <is>
           <t>Como capitán de equipo, quiero inscribir mi equipo en un torneo abierto, para competir por el trofeo y premio.</t>
         </is>
       </c>
-      <c r="L21" s="26" t="inlineStr">
+      <c r="L21" s="28" t="inlineStr">
         <is>
           <t>POST /api/torneos/{id}/inscribir</t>
         </is>
       </c>
-      <c r="M21" s="26" t="inlineStr">
+      <c r="M21" s="28" t="inlineStr">
         <is>
           <t>Torneos.tsx</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>HU-13</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="26" t="inlineStr">
         <is>
           <t>Dock Lateral: Modo Oscuro y Modo Claro</t>
         </is>
       </c>
-      <c r="D22" s="30" t="inlineStr">
+      <c r="D22" s="33" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
@@ -4335,104 +4343,104 @@
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="I22" s="25" t="inlineStr">
+      <c r="I22" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="J22" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K22" s="24" t="inlineStr">
+      <c r="K22" s="26" t="inlineStr">
         <is>
           <t>Como usuario, quiero alternar entre tema oscuro y claro desde un botón elegante a la derecha, para cuidar mi vista.</t>
         </is>
       </c>
-      <c r="L22" s="24" t="inlineStr">
+      <c r="L22" s="26" t="inlineStr">
         <is>
           <t>Client-side Theme</t>
         </is>
       </c>
-      <c r="M22" s="24" t="inlineStr">
+      <c r="M22" s="26" t="inlineStr">
         <is>
           <t>ThemeJoystick.tsx</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>HU-14</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
+      <c r="C23" s="28" t="inlineStr">
         <is>
           <t>Dock Lateral: Modo Celular Interactivo</t>
         </is>
       </c>
-      <c r="D23" s="31" t="inlineStr">
+      <c r="D23" s="34" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>UI / UX</t>
         </is>
       </c>
-      <c r="F23" s="13" t="inlineStr">
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="G23" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H23" s="13" t="inlineStr">
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="I23" s="25" t="inlineStr">
+      <c r="I23" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J23" s="14" t="inlineStr">
+      <c r="J23" s="16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K23" s="26" t="inlineStr">
+      <c r="K23" s="28" t="inlineStr">
         <is>
           <t>Como usuario o evaluador, quiero simular la vista en un marco de smartphone con dynamic island, para probar responsividad.</t>
         </is>
       </c>
-      <c r="L23" s="26" t="inlineStr">
+      <c r="L23" s="28" t="inlineStr">
         <is>
           <t>Client-side Viewport</t>
         </is>
       </c>
-      <c r="M23" s="26" t="inlineStr">
+      <c r="M23" s="28" t="inlineStr">
         <is>
           <t>ThemeJoystick.tsx</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>HU-15</t>
         </is>
       </c>
-      <c r="C24" s="24" t="inlineStr">
+      <c r="C24" s="26" t="inlineStr">
         <is>
           <t>Dock Lateral: Modo Computador (PC)</t>
         </is>
       </c>
-      <c r="D24" s="30" t="inlineStr">
+      <c r="D24" s="33" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
@@ -4455,344 +4463,344 @@
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="I24" s="25" t="inlineStr">
+      <c r="I24" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr">
+      <c r="J24" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K24" s="24" t="inlineStr">
+      <c r="K24" s="26" t="inlineStr">
         <is>
           <t>Como usuario de escritorio, quiero regresar a la vista panorámica de PC con un clic, para ver todo el contenido.</t>
         </is>
       </c>
-      <c r="L24" s="24" t="inlineStr">
+      <c r="L24" s="26" t="inlineStr">
         <is>
           <t>Client-side Viewport</t>
         </is>
       </c>
-      <c r="M24" s="24" t="inlineStr">
+      <c r="M24" s="26" t="inlineStr">
         <is>
           <t>ThemeJoystick.tsx</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>HU-16</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
-        <is>
-          <t>Tablón de Retos y Búsqueda de Rivales</t>
-        </is>
-      </c>
-      <c r="D25" s="31" t="inlineStr">
+      <c r="C25" s="28" t="inlineStr">
+        <is>
+          <t>Pasarela de Pagos Online PSE / Wompi</t>
+        </is>
+      </c>
+      <c r="D25" s="34" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>Comunidad</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>Pagos</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="I25" s="29" t="inlineStr">
+        <is>
+          <t>En Progreso</t>
+        </is>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K25" s="28" t="inlineStr">
+        <is>
+          <t>Como cliente, quiero pagar mi reserva en línea con tarjeta débito/crédito o PSE en pasarela bancaria en vivo.</t>
+        </is>
+      </c>
+      <c r="L25" s="28" t="inlineStr">
+        <is>
+          <t>Integración Pasarela API</t>
+        </is>
+      </c>
+      <c r="M25" s="28" t="inlineStr">
+        <is>
+          <t>PasarelaPago.tsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>HU-17</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>Descarga de Comprobante PDF con Código QR</t>
+        </is>
+      </c>
+      <c r="D26" s="33" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Comprobantes</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="I26" s="29" t="inlineStr">
+        <is>
+          <t>En Progreso</t>
+        </is>
+      </c>
+      <c r="J26" s="12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K26" s="26" t="inlineStr">
+        <is>
+          <t>Como cliente con reserva confirmada, quiero descargar un tiquete en PDF con código QR para mostrar en recepción.</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="inlineStr">
+        <is>
+          <t>Generador PDF Backend</t>
+        </is>
+      </c>
+      <c r="M26" s="26" t="inlineStr">
+        <is>
+          <t>ComprobanteReserva.tsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>HU-18</t>
+        </is>
+      </c>
+      <c r="C27" s="28" t="inlineStr">
+        <is>
+          <t>Notificaciones de Recordatorio por SMS / WhatsApp</t>
+        </is>
+      </c>
+      <c r="D27" s="34" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>Notificaciones</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="G27" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="H25" s="13" t="inlineStr">
+      <c r="H27" s="14" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="I25" s="25" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-      <c r="J25" s="14" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K25" s="26" t="inlineStr">
-        <is>
-          <t>Como jugador sin equipo completo, quiero publicar retos en el tablón de la sede, para encontrar rivales o jugadores.</t>
-        </is>
-      </c>
-      <c r="L25" s="26" t="inlineStr">
-        <is>
-          <t>Client-side State</t>
-        </is>
-      </c>
-      <c r="M25" s="26" t="inlineStr">
-        <is>
-          <t>TablonRetos.tsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>HU-17</t>
-        </is>
-      </c>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>Galería Acordeón Visual de Canchas</t>
-        </is>
-      </c>
-      <c r="D26" s="30" t="inlineStr">
+      <c r="I27" s="29" t="inlineStr">
+        <is>
+          <t>En Progreso</t>
+        </is>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K27" s="28" t="inlineStr">
+        <is>
+          <t>Como cliente, quiero recibir un mensaje de recordatorio 2 horas antes de mi partido programado.</t>
+        </is>
+      </c>
+      <c r="L27" s="28" t="inlineStr">
+        <is>
+          <t>Twilio / Meta API</t>
+        </is>
+      </c>
+      <c r="M27" s="28" t="inlineStr">
+        <is>
+          <t>ServicioRecordatorios.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>HU-19</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>Sistema de Puntos y Fidelización de Jugadores</t>
+        </is>
+      </c>
+      <c r="D28" s="33" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>UI / UX</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="n">
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Fidelización</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="I28" s="29" t="inlineStr">
+        <is>
+          <t>En Progreso</t>
+        </is>
+      </c>
+      <c r="J28" s="12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K28" s="26" t="inlineStr">
+        <is>
+          <t>Como cliente frecuente, quiero acumular puntos por cada hora jugada para canjear por horas gratis.</t>
+        </is>
+      </c>
+      <c r="L28" s="26" t="inlineStr">
+        <is>
+          <t>Módulo Puntos DB</t>
+        </is>
+      </c>
+      <c r="M28" s="26" t="inlineStr">
+        <is>
+          <t>PuntosCliente.tsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>HU-20</t>
+        </is>
+      </c>
+      <c r="C29" s="28" t="inlineStr">
+        <is>
+          <t>Sincronización con Google Calendar</t>
+        </is>
+      </c>
+      <c r="D29" s="34" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>Integraciones</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H29" s="14" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="I26" s="25" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-      <c r="J26" s="11" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K26" s="24" t="inlineStr">
-        <is>
-          <t>Como cliente, quiero ver imágenes dinámicas con iluminación LED y césped sintético, para motivarme a reservar.</t>
-        </is>
-      </c>
-      <c r="L26" s="24" t="inlineStr">
-        <is>
-          <t>Client-side Showcase</t>
-        </is>
-      </c>
-      <c r="M26" s="24" t="inlineStr">
-        <is>
-          <t>AcordeonCanchas.tsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>HU-18</t>
-        </is>
-      </c>
-      <c r="C27" s="26" t="inlineStr">
-        <is>
-          <t>Calificaciones y Reseñas con Estrellas</t>
-        </is>
-      </c>
-      <c r="D27" s="31" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>Reseñas</t>
-        </is>
-      </c>
-      <c r="F27" s="13" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="G27" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="H27" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="I27" s="25" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-      <c r="J27" s="14" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K27" s="26" t="inlineStr">
-        <is>
-          <t>Como cliente, quiero calificar las canchas con estrellas (1-5) y comentarios, para recomendar la sede.</t>
-        </is>
-      </c>
-      <c r="L27" s="26" t="inlineStr">
-        <is>
-          <t>GET/POST /api/resenas/</t>
-        </is>
-      </c>
-      <c r="M27" s="26" t="inlineStr">
-        <is>
-          <t>ResenasModal.tsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>HU-19</t>
-        </is>
-      </c>
-      <c r="C28" s="24" t="inlineStr">
-        <is>
-          <t>Contacto Inmediato vía WhatsApp</t>
-        </is>
-      </c>
-      <c r="D28" s="30" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>Soporte</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="I28" s="25" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-      <c r="J28" s="11" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K28" s="24" t="inlineStr">
-        <is>
-          <t>Como cliente, quiero un botón para escribir directo al WhatsApp de la sede, para resolver dudas rápidas.</t>
-        </is>
-      </c>
-      <c r="L28" s="24" t="inlineStr">
-        <is>
-          <t>WhatsApp API Link</t>
-        </is>
-      </c>
-      <c r="M28" s="24" t="inlineStr">
-        <is>
-          <t>AcordeonCanchas.tsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>HU-20</t>
-        </is>
-      </c>
-      <c r="C29" s="26" t="inlineStr">
-        <is>
-          <t>Barra de Fortaleza de Contraseña</t>
-        </is>
-      </c>
-      <c r="D29" s="31" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>Seguridad</t>
-        </is>
-      </c>
-      <c r="F29" s="13" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="G29" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H29" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 1</t>
-        </is>
-      </c>
-      <c r="I29" s="25" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-      <c r="J29" s="14" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K29" s="26" t="inlineStr">
-        <is>
-          <t>Como usuario al crear o cambiar clave, quiero ver un indicador visual de qué tan segura es mi contraseña.</t>
-        </is>
-      </c>
-      <c r="L29" s="26" t="inlineStr">
-        <is>
-          <t>Client-side Validator</t>
-        </is>
-      </c>
-      <c r="M29" s="26" t="inlineStr">
-        <is>
-          <t>RecuperarPasswordModal.tsx</t>
+      <c r="I29" s="29" t="inlineStr">
+        <is>
+          <t>En Progreso</t>
+        </is>
+      </c>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K29" s="28" t="inlineStr">
+        <is>
+          <t>Como cliente, quiero un botón para añadir automáticamente el partido agendado a mi calendario de Google.</t>
+        </is>
+      </c>
+      <c r="L29" s="28" t="inlineStr">
+        <is>
+          <t>Google Calendar API</t>
+        </is>
+      </c>
+      <c r="M29" s="28" t="inlineStr">
+        <is>
+          <t>BotonCalendar.tsx</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>HU-21</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C30" s="26" t="inlineStr">
         <is>
           <t>Panel de Control Principal (Dashboard Admin)</t>
         </is>
       </c>
-      <c r="D30" s="32" t="inlineStr">
+      <c r="D30" s="35" t="inlineStr">
         <is>
           <t>Administrador</t>
         </is>
@@ -4815,104 +4823,104 @@
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="I30" s="25" t="inlineStr">
+      <c r="I30" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J30" s="11" t="inlineStr">
+      <c r="J30" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K30" s="24" t="inlineStr">
+      <c r="K30" s="26" t="inlineStr">
         <is>
           <t>Como administrador, quiero ver el resumen global de reservas, ingresos totales, usuarios y canchas activas en un panel.</t>
         </is>
       </c>
-      <c r="L30" s="24" t="inlineStr">
+      <c r="L30" s="26" t="inlineStr">
         <is>
           <t>GET /api/reportes/resumen</t>
         </is>
       </c>
-      <c r="M30" s="24" t="inlineStr">
+      <c r="M30" s="26" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>HU-22</t>
         </is>
       </c>
-      <c r="C31" s="26" t="inlineStr">
+      <c r="C31" s="28" t="inlineStr">
         <is>
           <t>Métricas Financieras e Ingresos en Tiempo Real</t>
         </is>
       </c>
-      <c r="D31" s="33" t="inlineStr">
+      <c r="D31" s="36" t="inlineStr">
         <is>
           <t>Administrador</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E31" s="14" t="inlineStr">
         <is>
           <t>Reportes</t>
         </is>
       </c>
-      <c r="F31" s="13" t="inlineStr">
+      <c r="F31" s="14" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="G31" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H31" s="13" t="inlineStr">
+      <c r="H31" s="14" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="I31" s="25" t="inlineStr">
+      <c r="I31" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J31" s="14" t="inlineStr">
+      <c r="J31" s="16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K31" s="26" t="inlineStr">
+      <c r="K31" s="28" t="inlineStr">
         <is>
           <t>Como administrador, quiero consultar el dinero recaudado en el mes y proyecciones, para evaluar la rentabilidad.</t>
         </is>
       </c>
-      <c r="L31" s="26" t="inlineStr">
+      <c r="L31" s="28" t="inlineStr">
         <is>
           <t>GET /api/reportes/resumen</t>
         </is>
       </c>
-      <c r="M31" s="26" t="inlineStr">
+      <c r="M31" s="28" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>HU-23</t>
         </is>
       </c>
-      <c r="C32" s="24" t="inlineStr">
+      <c r="C32" s="26" t="inlineStr">
         <is>
           <t>Exportación de Reportes a Excel (.xlsx / .csv)</t>
         </is>
       </c>
-      <c r="D32" s="32" t="inlineStr">
+      <c r="D32" s="35" t="inlineStr">
         <is>
           <t>Administrador</t>
         </is>
@@ -4935,104 +4943,104 @@
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="I32" s="25" t="inlineStr">
+      <c r="I32" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J32" s="11" t="inlineStr">
+      <c r="J32" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K32" s="24" t="inlineStr">
+      <c r="K32" s="26" t="inlineStr">
         <is>
           <t>Como administrador, quiero descargar la base de datos de reservas e ingresos en formato Excel, para contabilidad física.</t>
         </is>
       </c>
-      <c r="L32" s="24" t="inlineStr">
+      <c r="L32" s="26" t="inlineStr">
         <is>
           <t>Client Export / API</t>
         </is>
       </c>
-      <c r="M32" s="24" t="inlineStr">
+      <c r="M32" s="26" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>HU-24</t>
         </is>
       </c>
-      <c r="C33" s="26" t="inlineStr">
+      <c r="C33" s="28" t="inlineStr">
         <is>
           <t>Creación y Registro de Nuevas Canchas</t>
         </is>
       </c>
-      <c r="D33" s="33" t="inlineStr">
+      <c r="D33" s="36" t="inlineStr">
         <is>
           <t>Administrador</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E33" s="14" t="inlineStr">
         <is>
           <t>Canchas</t>
         </is>
       </c>
-      <c r="F33" s="13" t="inlineStr">
+      <c r="F33" s="14" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="G33" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H33" s="13" t="inlineStr">
+      <c r="H33" s="14" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="I33" s="25" t="inlineStr">
+      <c r="I33" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J33" s="14" t="inlineStr">
+      <c r="J33" s="16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K33" s="26" t="inlineStr">
+      <c r="K33" s="28" t="inlineStr">
         <is>
           <t>Como administrador, quiero agregar nuevas canchas con su tipo, capacidad, precio/hora y servicios, para ampliar la oferta.</t>
         </is>
       </c>
-      <c r="L33" s="26" t="inlineStr">
+      <c r="L33" s="28" t="inlineStr">
         <is>
           <t>POST /api/canchas/</t>
         </is>
       </c>
-      <c r="M33" s="26" t="inlineStr">
+      <c r="M33" s="28" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>HU-25</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C34" s="26" t="inlineStr">
         <is>
           <t>Edición y Actualización de Tarifas de Canchas</t>
         </is>
       </c>
-      <c r="D34" s="32" t="inlineStr">
+      <c r="D34" s="35" t="inlineStr">
         <is>
           <t>Administrador</t>
         </is>
@@ -5055,104 +5063,104 @@
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="I34" s="25" t="inlineStr">
+      <c r="I34" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J34" s="11" t="inlineStr">
+      <c r="J34" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K34" s="24" t="inlineStr">
+      <c r="K34" s="26" t="inlineStr">
         <is>
           <t>Como administrador, quiero modificar los precios por hora y características de cada cancha, para ajustar promociones.</t>
         </is>
       </c>
-      <c r="L34" s="24" t="inlineStr">
+      <c r="L34" s="26" t="inlineStr">
         <is>
           <t>PUT /api/canchas/{id}</t>
         </is>
       </c>
-      <c r="M34" s="24" t="inlineStr">
+      <c r="M34" s="26" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>HU-26</t>
         </is>
       </c>
-      <c r="C35" s="26" t="inlineStr">
+      <c r="C35" s="28" t="inlineStr">
         <is>
           <t>Desactivación / Mantenimiento de Canchas</t>
         </is>
       </c>
-      <c r="D35" s="33" t="inlineStr">
+      <c r="D35" s="36" t="inlineStr">
         <is>
           <t>Administrador</t>
         </is>
       </c>
-      <c r="E35" s="13" t="inlineStr">
+      <c r="E35" s="14" t="inlineStr">
         <is>
           <t>Canchas</t>
         </is>
       </c>
-      <c r="F35" s="13" t="inlineStr">
+      <c r="F35" s="14" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="G35" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="H35" s="13" t="inlineStr">
+      <c r="H35" s="14" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="I35" s="25" t="inlineStr">
+      <c r="I35" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J35" s="14" t="inlineStr">
+      <c r="J35" s="16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K35" s="26" t="inlineStr">
+      <c r="K35" s="28" t="inlineStr">
         <is>
           <t>Como administrador, quiero deshabilitar temporalmente una cancha en mantenimiento, para que los clientes no la reserven.</t>
         </is>
       </c>
-      <c r="L35" s="26" t="inlineStr">
+      <c r="L35" s="28" t="inlineStr">
         <is>
           <t>PUT /api/canchas/{id}</t>
         </is>
       </c>
-      <c r="M35" s="26" t="inlineStr">
+      <c r="M35" s="28" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>HU-27</t>
         </is>
       </c>
-      <c r="C36" s="24" t="inlineStr">
+      <c r="C36" s="26" t="inlineStr">
         <is>
           <t>Eliminación Segura de Canchas</t>
         </is>
       </c>
-      <c r="D36" s="32" t="inlineStr">
+      <c r="D36" s="35" t="inlineStr">
         <is>
           <t>Administrador</t>
         </is>
@@ -5175,104 +5183,104 @@
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="I36" s="25" t="inlineStr">
+      <c r="I36" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr">
+      <c r="J36" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K36" s="24" t="inlineStr">
+      <c r="K36" s="26" t="inlineStr">
         <is>
           <t>Como administrador, quiero dar de baja canchas obsoletas con confirmación de seguridad.</t>
         </is>
       </c>
-      <c r="L36" s="24" t="inlineStr">
+      <c r="L36" s="26" t="inlineStr">
         <is>
           <t>DELETE /api/canchas/{id}</t>
         </is>
       </c>
-      <c r="M36" s="24" t="inlineStr">
+      <c r="M36" s="26" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="14" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>HU-28</t>
         </is>
       </c>
-      <c r="C37" s="26" t="inlineStr">
+      <c r="C37" s="28" t="inlineStr">
         <is>
           <t>Gestión Completa de Reservas Globales</t>
         </is>
       </c>
-      <c r="D37" s="33" t="inlineStr">
+      <c r="D37" s="36" t="inlineStr">
         <is>
           <t>Administrador</t>
         </is>
       </c>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="E37" s="14" t="inlineStr">
         <is>
           <t>Reservas</t>
         </is>
       </c>
-      <c r="F37" s="13" t="inlineStr">
+      <c r="F37" s="14" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="G37" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H37" s="13" t="inlineStr">
+      <c r="H37" s="14" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="I37" s="25" t="inlineStr">
+      <c r="I37" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J37" s="14" t="inlineStr">
+      <c r="J37" s="16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K37" s="26" t="inlineStr">
+      <c r="K37" s="28" t="inlineStr">
         <is>
           <t>Como administrador, quiero ver la lista de todas las reservas de todos los clientes con filtros por fecha y cancha.</t>
         </is>
       </c>
-      <c r="L37" s="26" t="inlineStr">
+      <c r="L37" s="28" t="inlineStr">
         <is>
           <t>GET /api/reservas/</t>
         </is>
       </c>
-      <c r="M37" s="26" t="inlineStr">
+      <c r="M37" s="28" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>HU-29</t>
         </is>
       </c>
-      <c r="C38" s="24" t="inlineStr">
+      <c r="C38" s="26" t="inlineStr">
         <is>
           <t>Cambio de Estado de Reserva (Confirmar / Completar)</t>
         </is>
       </c>
-      <c r="D38" s="32" t="inlineStr">
+      <c r="D38" s="35" t="inlineStr">
         <is>
           <t>Administrador</t>
         </is>
@@ -5295,104 +5303,104 @@
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="I38" s="25" t="inlineStr">
+      <c r="I38" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J38" s="11" t="inlineStr">
+      <c r="J38" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K38" s="24" t="inlineStr">
+      <c r="K38" s="26" t="inlineStr">
         <is>
           <t>Como administrador, quiero marcar reservas como pagadas, completadas o canceladas al llegar los jugadores a la sede.</t>
         </is>
       </c>
-      <c r="L38" s="24" t="inlineStr">
+      <c r="L38" s="26" t="inlineStr">
         <is>
           <t>PUT /api/reservas/{id}/estado</t>
         </is>
       </c>
-      <c r="M38" s="24" t="inlineStr">
+      <c r="M38" s="26" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>HU-30</t>
         </is>
       </c>
-      <c r="C39" s="26" t="inlineStr">
+      <c r="C39" s="28" t="inlineStr">
         <is>
           <t>Registro y Alta de Empleados de la Sede</t>
         </is>
       </c>
-      <c r="D39" s="33" t="inlineStr">
+      <c r="D39" s="36" t="inlineStr">
         <is>
           <t>Administrador</t>
         </is>
       </c>
-      <c r="E39" s="13" t="inlineStr">
+      <c r="E39" s="14" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="F39" s="13" t="inlineStr">
+      <c r="F39" s="14" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="G39" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H39" s="13" t="inlineStr">
+      <c r="H39" s="14" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="I39" s="25" t="inlineStr">
+      <c r="I39" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J39" s="14" t="inlineStr">
+      <c r="J39" s="16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K39" s="26" t="inlineStr">
+      <c r="K39" s="28" t="inlineStr">
         <is>
           <t>Como administrador, quiero registrar empleados (Coordinadores, Mantenimiento, Seguridad, Atención), para ordenar el personal.</t>
         </is>
       </c>
-      <c r="L39" s="26" t="inlineStr">
+      <c r="L39" s="28" t="inlineStr">
         <is>
           <t>POST /api/empleados/</t>
         </is>
       </c>
-      <c r="M39" s="26" t="inlineStr">
+      <c r="M39" s="28" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>HU-31</t>
         </is>
       </c>
-      <c r="C40" s="24" t="inlineStr">
+      <c r="C40" s="26" t="inlineStr">
         <is>
           <t>Listado y Edición del Personal</t>
         </is>
       </c>
-      <c r="D40" s="32" t="inlineStr">
+      <c r="D40" s="35" t="inlineStr">
         <is>
           <t>Administrador</t>
         </is>
@@ -5415,104 +5423,104 @@
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="I40" s="25" t="inlineStr">
+      <c r="I40" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr">
+      <c r="J40" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K40" s="24" t="inlineStr">
+      <c r="K40" s="26" t="inlineStr">
         <is>
           <t>Como administrador, quiero consultar el teléfono, correo y cargo de cada empleado y editar sus datos.</t>
         </is>
       </c>
-      <c r="L40" s="24" t="inlineStr">
+      <c r="L40" s="26" t="inlineStr">
         <is>
           <t>GET/PUT /api/empleados/</t>
         </is>
       </c>
-      <c r="M40" s="24" t="inlineStr">
+      <c r="M40" s="26" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="14" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>HU-32</t>
         </is>
       </c>
-      <c r="C41" s="26" t="inlineStr">
+      <c r="C41" s="28" t="inlineStr">
         <is>
           <t>Activación y Desactivación de Empleados</t>
         </is>
       </c>
-      <c r="D41" s="33" t="inlineStr">
+      <c r="D41" s="36" t="inlineStr">
         <is>
           <t>Administrador</t>
         </is>
       </c>
-      <c r="E41" s="13" t="inlineStr">
+      <c r="E41" s="14" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="F41" s="13" t="inlineStr">
+      <c r="F41" s="14" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="G41" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="H41" s="13" t="inlineStr">
+      <c r="H41" s="14" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="I41" s="25" t="inlineStr">
+      <c r="I41" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J41" s="14" t="inlineStr">
+      <c r="J41" s="16" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K41" s="26" t="inlineStr">
+      <c r="K41" s="28" t="inlineStr">
         <is>
           <t>Como administrador, quiero desactivar empleados inactivos sin perder el registro histórico.</t>
         </is>
       </c>
-      <c r="L41" s="26" t="inlineStr">
+      <c r="L41" s="28" t="inlineStr">
         <is>
           <t>PUT /api/empleados/{id}</t>
         </is>
       </c>
-      <c r="M41" s="26" t="inlineStr">
+      <c r="M41" s="28" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>HU-33</t>
         </is>
       </c>
-      <c r="C42" s="24" t="inlineStr">
+      <c r="C42" s="26" t="inlineStr">
         <is>
           <t>Creación y Apertura de Nuevos Torneos</t>
         </is>
       </c>
-      <c r="D42" s="32" t="inlineStr">
+      <c r="D42" s="35" t="inlineStr">
         <is>
           <t>Administrador</t>
         </is>
@@ -5535,111 +5543,111 @@
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="I42" s="25" t="inlineStr">
+      <c r="I42" s="27" t="inlineStr">
         <is>
           <t>Completado</t>
         </is>
       </c>
-      <c r="J42" s="11" t="inlineStr">
+      <c r="J42" s="12" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="K42" s="24" t="inlineStr">
+      <c r="K42" s="26" t="inlineStr">
         <is>
           <t>Como administrador, quiero crear torneos definiendo cancha sede, fechas, premio garantizado, valor y cupo máximo.</t>
         </is>
       </c>
-      <c r="L42" s="24" t="inlineStr">
+      <c r="L42" s="26" t="inlineStr">
         <is>
           <t>POST /api/torneos/</t>
         </is>
       </c>
-      <c r="M42" s="24" t="inlineStr">
+      <c r="M42" s="26" t="inlineStr">
         <is>
           <t>DashboardAdmin.tsx</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="14" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>HU-34</t>
         </is>
       </c>
-      <c r="C43" s="26" t="inlineStr">
-        <is>
-          <t>Cierre y Finalización de Torneos</t>
-        </is>
-      </c>
-      <c r="D43" s="33" t="inlineStr">
+      <c r="C43" s="28" t="inlineStr">
+        <is>
+          <t>Control de Acceso y Protección de Rutas RBAC</t>
+        </is>
+      </c>
+      <c r="D43" s="36" t="inlineStr">
         <is>
           <t>Administrador</t>
         </is>
       </c>
-      <c r="E43" s="13" t="inlineStr">
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="I43" s="27" t="inlineStr">
+        <is>
+          <t>Completado</t>
+        </is>
+      </c>
+      <c r="J43" s="16" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="K43" s="28" t="inlineStr">
+        <is>
+          <t>Como sistema, quiero bloquear el acceso al panel administrativo a usuarios no autenticados o con rol cliente (403 Forbidden).</t>
+        </is>
+      </c>
+      <c r="L43" s="28" t="inlineStr">
+        <is>
+          <t>Middleware Auth JWT</t>
+        </is>
+      </c>
+      <c r="M43" s="28" t="inlineStr">
+        <is>
+          <t>DashboardAdmin.tsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>HU-35</t>
+        </is>
+      </c>
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>Generador Automático de Cuadro de Llaves (Brackets)</t>
+        </is>
+      </c>
+      <c r="D44" s="35" t="inlineStr">
+        <is>
+          <t>Administrador</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
         <is>
           <t>Torneos</t>
-        </is>
-      </c>
-      <c r="F43" s="13" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="G43" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H43" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="I43" s="25" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-      <c r="J43" s="14" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="K43" s="26" t="inlineStr">
-        <is>
-          <t>Como administrador, quiero cambiar el estado de torneos de 'abierto' a 'en curso' o 'finalizado'.</t>
-        </is>
-      </c>
-      <c r="L43" s="26" t="inlineStr">
-        <is>
-          <t>PUT /api/torneos/{id}</t>
-        </is>
-      </c>
-      <c r="M43" s="26" t="inlineStr">
-        <is>
-          <t>DashboardAdmin.tsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="11" t="inlineStr">
-        <is>
-          <t>HU-35</t>
-        </is>
-      </c>
-      <c r="C44" s="24" t="inlineStr">
-        <is>
-          <t>Directorio de Clientes Registrados</t>
-        </is>
-      </c>
-      <c r="D44" s="32" t="inlineStr">
-        <is>
-          <t>Administrador</t>
-        </is>
-      </c>
-      <c r="E44" s="10" t="inlineStr">
-        <is>
-          <t>Usuarios</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
@@ -5652,114 +5660,114 @@
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
-          <t>Sprint 2</t>
-        </is>
-      </c>
-      <c r="I44" s="25" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-      <c r="J44" s="11" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K44" s="24" t="inlineStr">
-        <is>
-          <t>Como administrador, quiero ver el listado de todos los clientes registrados, sus correos y teléfonos de contacto.</t>
-        </is>
-      </c>
-      <c r="L44" s="24" t="inlineStr">
-        <is>
-          <t>GET /api/usuarios/clientes</t>
-        </is>
-      </c>
-      <c r="M44" s="24" t="inlineStr">
-        <is>
-          <t>DashboardAdmin.tsx</t>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="I44" s="29" t="inlineStr">
+        <is>
+          <t>En Progreso</t>
+        </is>
+      </c>
+      <c r="J44" s="12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K44" s="26" t="inlineStr">
+        <is>
+          <t>Como administrador, quiero que el sistema sortee y arme el cuadro de octavos y cuartos de final automáticamente.</t>
+        </is>
+      </c>
+      <c r="L44" s="26" t="inlineStr">
+        <is>
+          <t>Algoritmo Torneos</t>
+        </is>
+      </c>
+      <c r="M44" s="26" t="inlineStr">
+        <is>
+          <t>BracketsTorneo.tsx</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="14" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
         <is>
           <t>HU-36</t>
         </is>
       </c>
-      <c r="C45" s="26" t="inlineStr">
-        <is>
-          <t>Control de Acceso y Protección de Rutas RBAC</t>
-        </is>
-      </c>
-      <c r="D45" s="33" t="inlineStr">
+      <c r="C45" s="28" t="inlineStr">
+        <is>
+          <t>Lector y Validador de Códigos QR en Portería</t>
+        </is>
+      </c>
+      <c r="D45" s="36" t="inlineStr">
         <is>
           <t>Administrador</t>
         </is>
       </c>
-      <c r="E45" s="13" t="inlineStr">
+      <c r="E45" s="14" t="inlineStr">
         <is>
           <t>Seguridad</t>
         </is>
       </c>
-      <c r="F45" s="13" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="G45" s="13" t="n">
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H45" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 1</t>
-        </is>
-      </c>
-      <c r="I45" s="25" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-      <c r="J45" s="14" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K45" s="26" t="inlineStr">
-        <is>
-          <t>Como sistema, quiero bloquear el acceso al panel administrativo a usuarios no autenticados o con rol cliente (403 Forbidden).</t>
-        </is>
-      </c>
-      <c r="L45" s="26" t="inlineStr">
-        <is>
-          <t>Middleware Auth JWT</t>
-        </is>
-      </c>
-      <c r="M45" s="26" t="inlineStr">
-        <is>
-          <t>DashboardAdmin.tsx</t>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="I45" s="29" t="inlineStr">
+        <is>
+          <t>En Progreso</t>
+        </is>
+      </c>
+      <c r="J45" s="16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K45" s="28" t="inlineStr">
+        <is>
+          <t>Como recepcionista o portero, quiero escanear el QR del tiquete del cliente para validar el ingreso a la cancha.</t>
+        </is>
+      </c>
+      <c r="L45" s="28" t="inlineStr">
+        <is>
+          <t>Escáner Cámara Web</t>
+        </is>
+      </c>
+      <c r="M45" s="28" t="inlineStr">
+        <is>
+          <t>ValidadorQR.tsx</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>HU-37</t>
         </is>
       </c>
-      <c r="C46" s="24" t="inlineStr">
-        <is>
-          <t>Base de Datos SQLite Nativa con Claves Foráneas</t>
-        </is>
-      </c>
-      <c r="D46" s="32" t="inlineStr">
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>Despliegue Continuo en Servidores Cloud (CI/CD)</t>
+        </is>
+      </c>
+      <c r="D46" s="35" t="inlineStr">
         <is>
           <t>Administrador</t>
         </is>
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>Arquitectura</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
@@ -5772,92 +5780,92 @@
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>Sprint 1</t>
-        </is>
-      </c>
-      <c r="I46" s="25" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K46" s="24" t="inlineStr">
-        <is>
-          <t>Como desarrollador, quiero una base de datos local SQLite con relaciones íntegras y soporte MySQL opcional, para portabilidad total.</t>
-        </is>
-      </c>
-      <c r="L46" s="24" t="inlineStr">
-        <is>
-          <t>SQLAlchemy ORM PRAGMA</t>
-        </is>
-      </c>
-      <c r="M46" s="24" t="inlineStr">
-        <is>
-          <t>database.py</t>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="I46" s="29" t="inlineStr">
+        <is>
+          <t>En Progreso</t>
+        </is>
+      </c>
+      <c r="J46" s="12" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K46" s="26" t="inlineStr">
+        <is>
+          <t>Como equipo de desarrollo, quiero configurar pipelines de CI/CD para despliegue automático en la nube con dominio .com.</t>
+        </is>
+      </c>
+      <c r="L46" s="26" t="inlineStr">
+        <is>
+          <t>GitHub Actions / Docker</t>
+        </is>
+      </c>
+      <c r="M46" s="26" t="inlineStr">
+        <is>
+          <t>Dockerfile</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="14" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>HU-38</t>
         </is>
       </c>
-      <c r="C47" s="26" t="inlineStr">
-        <is>
-          <t>Configuración SMTP Gmail para Notificaciones</t>
-        </is>
-      </c>
-      <c r="D47" s="33" t="inlineStr">
+      <c r="C47" s="28" t="inlineStr">
+        <is>
+          <t>Módulo de Auditoría y Registro de Logs de Cambios</t>
+        </is>
+      </c>
+      <c r="D47" s="36" t="inlineStr">
         <is>
           <t>Administrador</t>
         </is>
       </c>
-      <c r="E47" s="13" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="F47" s="13" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="G47" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="H47" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 1</t>
-        </is>
-      </c>
-      <c r="I47" s="25" t="inlineStr">
-        <is>
-          <t>Completado</t>
-        </is>
-      </c>
-      <c r="J47" s="14" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="K47" s="26" t="inlineStr">
-        <is>
-          <t>Como desarrollador, quiero un servicio de correo con servidor Gmail SMTP TLS 587, para despachar correos a bandejas reales.</t>
-        </is>
-      </c>
-      <c r="L47" s="26" t="inlineStr">
-        <is>
-          <t>smtplib + MIME HTML</t>
-        </is>
-      </c>
-      <c r="M47" s="26" t="inlineStr">
-        <is>
-          <t>email_service.py</t>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="I47" s="29" t="inlineStr">
+        <is>
+          <t>En Progreso</t>
+        </is>
+      </c>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K47" s="28" t="inlineStr">
+        <is>
+          <t>Como administrador general, quiero ver qué empleado modificó una tarifa o canceló una reserva con fecha y hora.</t>
+        </is>
+      </c>
+      <c r="L47" s="28" t="inlineStr">
+        <is>
+          <t>Tabla Auditoria DB</t>
+        </is>
+      </c>
+      <c r="M47" s="28" t="inlineStr">
+        <is>
+          <t>LogsAuditoria.tsx</t>
         </is>
       </c>
     </row>
